--- a/jogos/Lista de Jogos Finalizados.xlsx
+++ b/jogos/Lista de Jogos Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E15DA5-D5F6-4D33-8E3D-EDFF34880284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D45A5D6-65F0-4F5D-8775-09700687D542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{185F8663-3FF1-4EF9-AA90-43B25B82DF02}"/>
   </bookViews>
@@ -2253,6 +2253,19 @@
         </r>
       </text>
     </comment>
+    <comment ref="K335" authorId="0" shapeId="0" xr:uid="{AD5C0130-2017-4852-98DF-104DD282236B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Platina. 🏆</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K337" authorId="0" shapeId="0" xr:uid="{982E5468-694E-45B4-B854-D1B571F42C52}">
       <text>
         <r>
@@ -3173,9 +3186,6 @@
     <t>Super Metroid</t>
   </si>
   <si>
-    <t>Resident Evil - The Darkside Chronicles</t>
-  </si>
-  <si>
     <t>Metroid II - Return of Samus</t>
   </si>
   <si>
@@ -3228,9 +3238,6 @@
   </si>
   <si>
     <t>Metroid - Zero Mission</t>
-  </si>
-  <si>
-    <t>Dragon Ball - Advanced Adventure</t>
   </si>
   <si>
     <t>Super Mario Odyssey</t>
@@ -5403,6 +5410,12 @@
   </si>
   <si>
     <t>Ultra Street Fighter II The Final Challengers</t>
+  </si>
+  <si>
+    <t>Dragon Ball: Advanced Adventure</t>
+  </si>
+  <si>
+    <t>Resident Evil: The Darkside Chronicles</t>
   </si>
 </sst>
 </file>
@@ -6728,7 +6741,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E1" s="34" t="s">
         <v>2</v>
@@ -6740,7 +6753,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I1" s="34" t="s">
         <v>5</v>
@@ -6868,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="T3" s="38" t="s">
         <v>0</v>
@@ -6885,13 +6898,13 @@
         <v>384</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>65</v>
@@ -6915,7 +6928,7 @@
         <v>37</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N4" s="63">
         <f>COUNTIF(H:H,11)</f>
@@ -6949,13 +6962,13 @@
         <v>383</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>65</v>
@@ -6986,14 +6999,14 @@
         <v>58</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q5" s="15">
         <f>COUNTIF(C:C,"3DS")</f>
         <v>48</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T5" s="15">
         <f>COUNTIF(D:D,"Switch")</f>
@@ -7013,13 +7026,13 @@
         <v>382</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>30</v>
@@ -7050,14 +7063,14 @@
         <v>64</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q6" s="15">
         <f>COUNTIF(C:C,"Switch")</f>
         <v>41</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T6" s="15">
         <f>COUNTIF(D:D,"PS4")</f>
@@ -7077,13 +7090,13 @@
         <v>381</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>28</v>
@@ -7114,14 +7127,14 @@
         <v>90</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q7" s="15">
         <f>COUNTIF(C:C,"PS4")</f>
         <v>36</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="T7" s="15">
         <f>COUNTIF(D:D,"3DS")</f>
@@ -7141,16 +7154,16 @@
         <v>380</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" s="5">
         <v>46278</v>
@@ -7179,14 +7192,14 @@
         <v>90</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q8" s="15">
         <f>COUNTIF(C:C,"Switch 2")</f>
         <v>32</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="T8" s="15">
         <f>COUNTIF(D:D,"PS3")</f>
@@ -7206,13 +7219,13 @@
         <v>379</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
@@ -7243,14 +7256,14 @@
         <v>37</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q9" s="15">
         <f>COUNTIF(C:C,"PS3")</f>
         <v>31</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="T9" s="15">
         <f>COUNTIF(D:D,"DS")</f>
@@ -7270,13 +7283,13 @@
         <v>378</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>29</v>
@@ -7294,7 +7307,7 @@
         <v>33</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>38</v>
@@ -7307,14 +7320,14 @@
         <v>18</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Q10" s="15">
         <f>COUNTIF(C:C,"DS")</f>
         <v>21</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="T10" s="15">
         <f>COUNTIF(D:D,"GBA")</f>
@@ -7334,13 +7347,13 @@
         <v>377</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
@@ -7371,14 +7384,14 @@
         <v>7</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Q11" s="15">
         <f>COUNTIF(C:C,"Wii")</f>
         <v>11</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="T11" s="15">
         <f>COUNTIF(D:D,"N64")</f>
@@ -7398,13 +7411,13 @@
         <v>376</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
@@ -7435,14 +7448,14 @@
         <v>2</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q12" s="15">
         <f>COUNTIF(C:C,"SNES")</f>
         <v>11</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="T12" s="15">
         <f>COUNTIF(D:D,"SNES")</f>
@@ -7462,13 +7475,13 @@
         <v>375</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -7499,21 +7512,21 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="Q13" s="15">
         <f>COUNTIF(C:C,"Vita")</f>
         <v>10</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T13" s="15">
         <f>COUNTIF(D:D,"PS1")</f>
         <v>9</v>
       </c>
       <c r="V13" s="68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W13" s="69">
         <f>COUNTIF(E:E,"Beat Up")</f>
@@ -7526,13 +7539,13 @@
         <v>374</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>23</v>
@@ -7563,14 +7576,14 @@
         <v>1</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q14" s="15">
         <f>COUNTIF(C:C,"X 360")</f>
         <v>8</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="T14" s="15">
         <f>COUNTIF(D:D,"Vita")</f>
@@ -7590,13 +7603,13 @@
         <v>373</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -7614,7 +7627,7 @@
         <v>32</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>37</v>
@@ -7627,21 +7640,21 @@
         <v>384</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q15" s="15">
         <f>COUNTIF(C:C,"N64")</f>
         <v>7</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="T15" s="15">
         <f>COUNTIF(D:D,"GB")</f>
         <v>8</v>
       </c>
       <c r="V15" s="68" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="W15" s="69">
         <f>COUNTIF(E:E,"Tabuleiro")</f>
@@ -7654,13 +7667,13 @@
         <v>372</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>21</v>
@@ -7686,21 +7699,21 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="P16" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q16" s="15">
         <f>COUNTIF(C:C,"Wii U")</f>
         <v>7</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="T16" s="15">
         <f>COUNTIF(D:D,"X 360")</f>
         <v>8</v>
       </c>
       <c r="V16" s="41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="W16" s="42">
         <f>COUNTIF(E:E,"Puzzle")</f>
@@ -7713,13 +7726,13 @@
         <v>371</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>21</v>
@@ -7749,21 +7762,21 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="Q17" s="15">
         <f>COUNTIF(C:C,"GBA")</f>
         <v>6</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="T17" s="15">
         <f>COUNTIF(D:D,"Wii U")</f>
         <v>7</v>
       </c>
       <c r="V17" s="68" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="W17" s="69">
         <f>COUNTIF(E:E,"Simulador")</f>
@@ -7776,13 +7789,13 @@
         <v>370</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>21</v>
@@ -7813,14 +7826,14 @@
         <v>4</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q18" s="15">
         <f>COUNTIF(C:C,"X Series")</f>
         <v>6</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="T18" s="15">
         <f>COUNTIF(D:D,"Switch 2")</f>
@@ -7840,13 +7853,13 @@
         <v>369</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>21</v>
@@ -7877,21 +7890,21 @@
         <v>39</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q19" s="15">
         <f>COUNTIF(C:C,"GB")</f>
         <v>5</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T19" s="15">
         <f>COUNTIF(D:D,"Wii")</f>
         <v>6</v>
       </c>
       <c r="V19" s="68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="W19" s="69">
         <f>COUNTIF(E:E,"Sandbox")</f>
@@ -7904,13 +7917,13 @@
         <v>368</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>21</v>
@@ -7942,21 +7955,21 @@
         <v>252</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q20" s="15">
         <f>COUNTIF(C:C,"PS1")</f>
         <v>5</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="T20" s="15">
         <f>COUNTIF(D:D,"X Series")</f>
         <v>6</v>
       </c>
       <c r="V20" s="75" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W20" s="42">
         <f>COUNTIF(E:E,"Roguelike")</f>
@@ -7969,13 +7982,13 @@
         <v>367</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>22</v>
@@ -8006,21 +8019,21 @@
         <v>89</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q21" s="15">
         <f>COUNTIF(C:C,"PSP")</f>
         <v>5</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="T21" s="15">
         <f>COUNTIF(D:D,"GBC")</f>
         <v>6</v>
       </c>
       <c r="V21" s="70" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="W21" s="71">
         <f>COUNTIF(E:E,"Pinball")</f>
@@ -8033,13 +8046,13 @@
         <v>366</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>22</v>
@@ -8071,14 +8084,14 @@
         <v>384</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="Q22" s="15">
         <f>COUNTIF(C:C,"GC")</f>
         <v>4</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="T22" s="15">
         <f>COUNTIF(D:D,"PS2")</f>
@@ -8098,7 +8111,7 @@
         <v>365</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>20</v>
@@ -8128,14 +8141,14 @@
         <v>37</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q23" s="15">
         <f>COUNTIF(C:C,"GBC")</f>
         <v>3</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T23" s="15">
         <f>COUNTIF(D:D,"PSP")</f>
@@ -8148,13 +8161,13 @@
         <v>364</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>27</v>
@@ -8179,20 +8192,20 @@
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="43" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="N24" s="44" t="s">
         <v>51</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q24" s="15">
         <f>COUNTIF(C:C,"X One")</f>
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="T24" s="15">
         <f>COUNTIF(D:D,"GC")</f>
@@ -8205,7 +8218,7 @@
         <v>363</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8236,21 +8249,21 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="49" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N25" s="42">
         <f>COUNTIFS(B:B,"*[P]*")</f>
         <v>19</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q25" s="15">
         <f>COUNTIF(C:C,"PS2")</f>
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="T25" s="15">
         <f>COUNTIF(D:D,"MD")</f>
@@ -8263,13 +8276,13 @@
         <v>362</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>27</v>
@@ -8294,21 +8307,21 @@
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="48" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="N26" s="42">
         <f>COUNTIFS(B:B,"*[D]*")</f>
         <v>4</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Q26" s="15">
         <f>COUNTIF(C:C,"NES")</f>
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="T26" s="15">
         <f>COUNTIF(D:D,"NES")</f>
@@ -8321,13 +8334,13 @@
         <v>361</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>23</v>
@@ -8352,21 +8365,21 @@
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N27" s="42">
         <f>N29-N28</f>
         <v>332</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="Q27" s="15">
         <f>COUNTIF(C:C,"MD")</f>
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="T27" s="15">
         <f>COUNTIF(D:D,"X One")</f>
@@ -8379,7 +8392,7 @@
         <v>360</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>20</v>
@@ -8403,14 +8416,14 @@
         <v>32</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="46" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N28" s="42">
         <f>COUNTIFS(B:B,"*(*")</f>
@@ -8437,13 +8450,13 @@
         <v>359</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>21</v>
@@ -8467,7 +8480,7 @@
         <v>37</v>
       </c>
       <c r="M29" s="43" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N29" s="47">
         <f>COUNT(A:A)</f>
@@ -8480,13 +8493,13 @@
         <v>358</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
@@ -8519,7 +8532,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="T30" s="38" t="s">
         <v>0</v>
@@ -8531,13 +8544,13 @@
         <v>357</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>23</v>
@@ -8568,14 +8581,14 @@
         <v>0</v>
       </c>
       <c r="P31" s="33" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q31" s="15" cm="1">
         <f t="array" ref="Q31">SUM(SUMIF($P$4:$P$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$Q$4:$Q$27))</f>
         <v>196</v>
       </c>
       <c r="S31" s="33" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T31" s="15" cm="1">
         <f t="array" ref="T31">SUM(SUMIF($S$4:$S$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$T$4:$T$27))</f>
@@ -8588,13 +8601,13 @@
         <v>356</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>24</v>
@@ -8619,21 +8632,21 @@
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="52" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N32" s="42">
         <f>COUNTIF(K:K,"Sim")</f>
         <v>290</v>
       </c>
       <c r="P32" s="58" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Q32" s="15" cm="1">
         <f t="array" ref="Q32">SUM(SUMIF($P$4:$P$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$Q$4:$Q$27))</f>
         <v>87</v>
       </c>
       <c r="S32" s="58" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T32" s="15" cm="1">
         <f t="array" ref="T32">SUM(SUMIF($S$4:$S$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$T$4:$T$27))</f>
@@ -8646,13 +8659,13 @@
         <v>355</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>23</v>
@@ -8677,21 +8690,21 @@
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="53" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N33" s="42">
         <f>COUNTIF(K:K,"Não")</f>
         <v>94</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q33" s="15" cm="1">
         <f t="array" ref="Q33">SUM(SUMIF($P$4:$P$27,{"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>15</v>
       </c>
       <c r="S33" s="59" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="T33" s="15" cm="1">
         <f t="array" ref="T33">SUM(SUMIF($S$4:$S$27,{"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8704,13 +8717,13 @@
         <v>354</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>27</v>
@@ -8762,13 +8775,13 @@
         <v>353</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>24</v>
@@ -8795,14 +8808,14 @@
       <c r="M35"/>
       <c r="N35"/>
       <c r="P35" s="62" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q35" s="15" cm="1">
         <f t="array" ref="Q35">SUM($Q$4:$Q$27)-SUM(SUMIF($P$4:$P$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>0</v>
       </c>
       <c r="S35" s="62" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="T35" s="15" cm="1">
         <f t="array" ref="T35">SUM($T$4:$T$27)-SUM(SUMIF($S$4:$S$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8815,13 +8828,13 @@
         <v>352</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>29</v>
@@ -8868,13 +8881,13 @@
         <v>351</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>23</v>
@@ -8908,13 +8921,13 @@
         <v>350</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>65</v>
@@ -8942,10 +8955,10 @@
         <v>53</v>
       </c>
       <c r="N38" s="55" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="O38" s="82" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P38" s="83"/>
     </row>
@@ -8955,13 +8968,13 @@
         <v>349</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>22</v>
@@ -8993,7 +9006,7 @@
         <v>25</v>
       </c>
       <c r="O39" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M39,1,1), $F:$F, "&lt;="&amp;DATE(M39,12,31))</f>
+        <f t="shared" ref="O39:O51" si="0">SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M39,1,1), $F:$F, "&lt;="&amp;DATE(M39,12,31))</f>
         <v>21.632210648148149</v>
       </c>
       <c r="P39" s="77"/>
@@ -9004,13 +9017,13 @@
         <v>348</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
@@ -9042,7 +9055,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M40,1,1), $F:$F, "&lt;="&amp;DATE(M40,12,31))</f>
+        <f t="shared" si="0"/>
         <v>39.712557870370361</v>
       </c>
       <c r="P40" s="79"/>
@@ -9053,13 +9066,13 @@
         <v>347</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>21</v>
@@ -9091,7 +9104,7 @@
         <v>24</v>
       </c>
       <c r="O41" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M41,1,1), $F:$F, "&lt;="&amp;DATE(M41,12,31))</f>
+        <f t="shared" si="0"/>
         <v>15.460520833333334</v>
       </c>
       <c r="P41" s="77"/>
@@ -9102,13 +9115,13 @@
         <v>346</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>23</v>
@@ -9140,7 +9153,7 @@
         <v>35</v>
       </c>
       <c r="O42" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M42,1,1), $F:$F, "&lt;="&amp;DATE(M42,12,31))</f>
+        <f t="shared" si="0"/>
         <v>66.78905092592592</v>
       </c>
       <c r="P42" s="79"/>
@@ -9151,13 +9164,13 @@
         <v>345</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>23</v>
@@ -9188,8 +9201,8 @@
         <v>33</v>
       </c>
       <c r="O43" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M43,1,1), $F:$F, "&lt;="&amp;DATE(M43,12,31))</f>
-        <v>57.577337962962957</v>
+        <f t="shared" si="0"/>
+        <v>58.889837962962957</v>
       </c>
       <c r="P43" s="77"/>
     </row>
@@ -9199,13 +9212,13 @@
         <v>344</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>28</v>
@@ -9236,8 +9249,8 @@
         <v>20</v>
       </c>
       <c r="O44" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M44,1,1), $F:$F, "&lt;="&amp;DATE(M44,12,31))</f>
-        <v>40.908263888888882</v>
+        <f t="shared" si="0"/>
+        <v>47.408263888888897</v>
       </c>
       <c r="P44" s="79"/>
     </row>
@@ -9247,16 +9260,16 @@
         <v>343</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F45" s="5">
         <v>45680</v>
@@ -9271,7 +9284,7 @@
         <v>33</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>37</v>
@@ -9284,8 +9297,8 @@
         <v>29</v>
       </c>
       <c r="O45" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M45,1,1), $F:$F, "&lt;="&amp;DATE(M45,12,31))</f>
-        <v>55.715277777777771</v>
+        <f t="shared" si="0"/>
+        <v>63.090277777777764</v>
       </c>
       <c r="P45" s="77"/>
     </row>
@@ -9295,13 +9308,13 @@
         <v>342</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>21</v>
@@ -9332,8 +9345,8 @@
         <v>20</v>
       </c>
       <c r="O46" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M46,1,1), $F:$F, "&lt;="&amp;DATE(M46,12,31))</f>
-        <v>50.021655092592589</v>
+        <f t="shared" si="0"/>
+        <v>57.896655092592589</v>
       </c>
       <c r="P46" s="79"/>
     </row>
@@ -9343,13 +9356,13 @@
         <v>341</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>21</v>
@@ -9380,8 +9393,8 @@
         <v>50</v>
       </c>
       <c r="O47" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M47,1,1), $F:$F, "&lt;="&amp;DATE(M47,12,31))</f>
-        <v>76.243229166666666</v>
+        <f t="shared" si="0"/>
+        <v>96.097395833333323</v>
       </c>
       <c r="P47" s="77"/>
     </row>
@@ -9391,13 +9404,13 @@
         <v>340</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>23</v>
@@ -9428,8 +9441,8 @@
         <v>50</v>
       </c>
       <c r="O48" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M48,1,1), $F:$F, "&lt;="&amp;DATE(M48,12,31))</f>
-        <v>47.410439814814822</v>
+        <f t="shared" si="0"/>
+        <v>76.722939814814836</v>
       </c>
       <c r="P48" s="79"/>
     </row>
@@ -9439,7 +9452,7 @@
         <v>339</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>20</v>
@@ -9476,8 +9489,8 @@
         <v>20</v>
       </c>
       <c r="O49" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M49,1,1), $F:$F, "&lt;="&amp;DATE(M49,12,31))</f>
-        <v>4.1527777777777777</v>
+        <f t="shared" si="0"/>
+        <v>29.277777777777782</v>
       </c>
       <c r="P49" s="77"/>
     </row>
@@ -9487,7 +9500,7 @@
         <v>338</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>20</v>
@@ -9511,7 +9524,7 @@
         <v>32</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>37</v>
@@ -9524,8 +9537,8 @@
         <v>42</v>
       </c>
       <c r="O50" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M50,1,1), $F:$F, "&lt;="&amp;DATE(M50,12,31))</f>
-        <v>14.897916666666667</v>
+        <f t="shared" si="0"/>
+        <v>33.481250000000003</v>
       </c>
       <c r="P50" s="79"/>
     </row>
@@ -9535,13 +9548,13 @@
         <v>337</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>30</v>
@@ -9572,8 +9585,8 @@
         <v>16</v>
       </c>
       <c r="O51" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M51,1,1), $F:$F, "&lt;="&amp;DATE(M51,12,31))</f>
-        <v>18.109722222222224</v>
+        <f t="shared" si="0"/>
+        <v>40.547222222222231</v>
       </c>
       <c r="P51" s="77"/>
     </row>
@@ -9583,7 +9596,7 @@
         <v>336</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>20</v>
@@ -9621,7 +9634,7 @@
       </c>
       <c r="O52" s="80">
         <f>SUM(O39:P51)</f>
-        <v>508.63096064814812</v>
+        <v>647.00596064814829</v>
       </c>
       <c r="P52" s="81"/>
     </row>
@@ -9631,13 +9644,13 @@
         <v>335</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>69</v>
@@ -9655,7 +9668,7 @@
         <v>32</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>38</v>
@@ -9667,13 +9680,13 @@
         <v>334</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>69</v>
@@ -9691,7 +9704,7 @@
         <v>32</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>38</v>
@@ -9703,13 +9716,13 @@
         <v>333</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>69</v>
@@ -9727,7 +9740,7 @@
         <v>32</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>38</v>
@@ -9739,13 +9752,13 @@
         <v>332</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>69</v>
@@ -9763,7 +9776,7 @@
         <v>32</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>38</v>
@@ -9775,13 +9788,13 @@
         <v>331</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>69</v>
@@ -9799,7 +9812,7 @@
         <v>32</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>38</v>
@@ -9811,13 +9824,13 @@
         <v>330</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>69</v>
@@ -9835,7 +9848,7 @@
         <v>32</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>38</v>
@@ -9847,13 +9860,13 @@
         <v>329</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>22</v>
@@ -9883,13 +9896,13 @@
         <v>328</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>69</v>
@@ -9907,7 +9920,7 @@
         <v>32</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>38</v>
@@ -9919,13 +9932,13 @@
         <v>327</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>69</v>
@@ -9943,7 +9956,7 @@
         <v>32</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>37</v>
@@ -9955,13 +9968,13 @@
         <v>326</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
@@ -9991,7 +10004,7 @@
         <v>325</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>20</v>
@@ -10027,7 +10040,7 @@
         <v>324</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>20</v>
@@ -10063,7 +10076,7 @@
         <v>323</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>20</v>
@@ -10099,7 +10112,7 @@
         <v>322</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>20</v>
@@ -10135,7 +10148,7 @@
         <v>321</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>20</v>
@@ -10144,7 +10157,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F67" s="5">
         <v>45314</v>
@@ -10159,7 +10172,7 @@
         <v>32</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>37</v>
@@ -10171,7 +10184,7 @@
         <v>320</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>20</v>
@@ -10207,7 +10220,7 @@
         <v>319</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>20</v>
@@ -10243,7 +10256,7 @@
         <v>318</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
@@ -10252,7 +10265,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F70" s="5">
         <v>45303</v>
@@ -10267,7 +10280,7 @@
         <v>33</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>37</v>
@@ -10279,13 +10292,13 @@
         <v>317</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>22</v>
@@ -10315,13 +10328,13 @@
         <v>316</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>27</v>
@@ -10351,7 +10364,7 @@
         <v>315</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>20</v>
@@ -10360,7 +10373,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F73" s="5">
         <v>45286</v>
@@ -10375,7 +10388,7 @@
         <v>33</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>37</v>
@@ -10387,13 +10400,13 @@
         <v>314</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>69</v>
@@ -10411,7 +10424,7 @@
         <v>33</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>38</v>
@@ -10423,16 +10436,16 @@
         <v>313</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F75" s="5">
         <v>45260</v>
@@ -10447,7 +10460,7 @@
         <v>34</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>38</v>
@@ -10459,13 +10472,13 @@
         <v>312</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>21</v>
@@ -10495,7 +10508,7 @@
         <v>311</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>20</v>
@@ -10531,13 +10544,13 @@
         <v>310</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>21</v>
@@ -10567,13 +10580,13 @@
         <v>309</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>23</v>
@@ -10603,13 +10616,13 @@
         <v>308</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>21</v>
@@ -10639,13 +10652,13 @@
         <v>307</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>21</v>
@@ -10675,13 +10688,13 @@
         <v>306</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>23</v>
@@ -10711,13 +10724,13 @@
         <v>305</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>23</v>
@@ -10747,16 +10760,16 @@
         <v>304</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F84" s="5">
         <v>45176</v>
@@ -10783,13 +10796,13 @@
         <v>303</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>21</v>
@@ -10819,13 +10832,13 @@
         <v>302</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>21</v>
@@ -10855,13 +10868,13 @@
         <v>301</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>23</v>
@@ -10891,13 +10904,13 @@
         <v>300</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>23</v>
@@ -10927,13 +10940,13 @@
         <v>299</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>69</v>
@@ -10951,7 +10964,7 @@
         <v>33</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>38</v>
@@ -10963,13 +10976,13 @@
         <v>298</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>23</v>
@@ -10999,13 +11012,13 @@
         <v>297</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>22</v>
@@ -11035,16 +11048,16 @@
         <v>296</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F92" s="5">
         <v>45124</v>
@@ -11059,7 +11072,7 @@
         <v>34</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>37</v>
@@ -11071,16 +11084,16 @@
         <v>295</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F93" s="5">
         <v>45121</v>
@@ -11095,7 +11108,7 @@
         <v>32</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>37</v>
@@ -11107,13 +11120,13 @@
         <v>294</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>22</v>
@@ -11143,7 +11156,7 @@
         <v>293</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>20</v>
@@ -11179,13 +11192,13 @@
         <v>292</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>22</v>
@@ -11215,13 +11228,13 @@
         <v>291</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>21</v>
@@ -11251,13 +11264,13 @@
         <v>290</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>27</v>
@@ -11287,13 +11300,13 @@
         <v>289</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>30</v>
@@ -11311,7 +11324,7 @@
         <v>34</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>37</v>
@@ -11323,13 +11336,13 @@
         <v>288</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>30</v>
@@ -11347,7 +11360,7 @@
         <v>34</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>37</v>
@@ -11359,7 +11372,7 @@
         <v>287</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>20</v>
@@ -11395,7 +11408,7 @@
         <v>286</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>20</v>
@@ -11404,7 +11417,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F102" s="5">
         <v>45011</v>
@@ -11431,7 +11444,7 @@
         <v>285</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>20</v>
@@ -11467,13 +11480,13 @@
         <v>284</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>23</v>
@@ -11503,13 +11516,13 @@
         <v>283</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>23</v>
@@ -11539,13 +11552,13 @@
         <v>282</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>23</v>
@@ -11563,7 +11576,7 @@
         <v>52</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>37</v>
@@ -11575,13 +11588,13 @@
         <v>281</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>23</v>
@@ -11611,13 +11624,13 @@
         <v>280</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -11647,7 +11660,7 @@
         <v>279</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>20</v>
@@ -11683,7 +11696,7 @@
         <v>278</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>20</v>
@@ -11719,7 +11732,7 @@
         <v>277</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>20</v>
@@ -11755,7 +11768,7 @@
         <v>276</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>20</v>
@@ -11791,13 +11804,13 @@
         <v>275</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>24</v>
@@ -11827,7 +11840,7 @@
         <v>274</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>20</v>
@@ -11863,7 +11876,7 @@
         <v>273</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>20</v>
@@ -11899,7 +11912,7 @@
         <v>272</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>20</v>
@@ -11935,13 +11948,13 @@
         <v>271</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>23</v>
@@ -11971,7 +11984,7 @@
         <v>270</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>20</v>
@@ -12007,7 +12020,7 @@
         <v>269</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>20</v>
@@ -12043,7 +12056,7 @@
         <v>268</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>20</v>
@@ -12079,7 +12092,7 @@
         <v>267</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>20</v>
@@ -12115,7 +12128,7 @@
         <v>266</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>20</v>
@@ -12151,7 +12164,7 @@
         <v>265</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>20</v>
@@ -12160,7 +12173,7 @@
         <v>20</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F123" s="5">
         <v>44759</v>
@@ -12187,7 +12200,7 @@
         <v>264</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>20</v>
@@ -12196,7 +12209,7 @@
         <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F124" s="5">
         <v>44757</v>
@@ -12223,7 +12236,7 @@
         <v>263</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>20</v>
@@ -12259,7 +12272,7 @@
         <v>262</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>20</v>
@@ -12295,7 +12308,7 @@
         <v>261</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>20</v>
@@ -12331,7 +12344,7 @@
         <v>260</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>20</v>
@@ -12367,7 +12380,7 @@
         <v>259</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>20</v>
@@ -12403,7 +12416,7 @@
         <v>258</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>20</v>
@@ -12412,7 +12425,7 @@
         <v>20</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F130" s="5">
         <v>44717</v>
@@ -12439,7 +12452,7 @@
         <v>257</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>20</v>
@@ -12448,7 +12461,7 @@
         <v>20</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F131" s="5">
         <v>44695</v>
@@ -12475,7 +12488,7 @@
         <v>256</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>20</v>
@@ -12511,7 +12524,7 @@
         <v>255</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>20</v>
@@ -12547,7 +12560,7 @@
         <v>254</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>20</v>
@@ -12571,7 +12584,7 @@
         <v>32</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K134" s="1" t="s">
         <v>37</v>
@@ -12583,7 +12596,7 @@
         <v>253</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>20</v>
@@ -12619,7 +12632,7 @@
         <v>252</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>20</v>
@@ -12628,7 +12641,7 @@
         <v>20</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F136" s="5">
         <v>44678</v>
@@ -12655,7 +12668,7 @@
         <v>251</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>20</v>
@@ -12691,7 +12704,7 @@
         <v>250</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>20</v>
@@ -12700,7 +12713,7 @@
         <v>20</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F138" s="5">
         <v>44672</v>
@@ -12727,7 +12740,7 @@
         <v>249</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>20</v>
@@ -12742,7 +12755,7 @@
         <v>44652</v>
       </c>
       <c r="G139" s="28">
-        <v>0</v>
+        <v>1.3125</v>
       </c>
       <c r="H139" s="1">
         <v>11</v>
@@ -12763,13 +12776,13 @@
         <v>248</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>23</v>
@@ -12799,13 +12812,13 @@
         <v>247</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>23</v>
@@ -12835,16 +12848,16 @@
         <v>246</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F142" s="5">
         <v>44530</v>
@@ -12859,7 +12872,7 @@
         <v>33</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>38</v>
@@ -12871,13 +12884,13 @@
         <v>245</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>24</v>
@@ -12907,13 +12920,13 @@
         <v>244</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>24</v>
@@ -12943,22 +12956,22 @@
         <v>243</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F145" s="5">
         <v>44470</v>
       </c>
       <c r="G145" s="28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H145" s="1">
         <v>9</v>
@@ -12979,13 +12992,13 @@
         <v>242</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>29</v>
@@ -12994,7 +13007,7 @@
         <v>44444</v>
       </c>
       <c r="G146" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H146" s="1">
         <v>8</v>
@@ -13015,13 +13028,13 @@
         <v>241</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>23</v>
@@ -13030,7 +13043,7 @@
         <v>44443</v>
       </c>
       <c r="G147" s="28">
-        <v>0</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="H147" s="1">
         <v>8</v>
@@ -13051,22 +13064,22 @@
         <v>240</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F148" s="5">
         <v>44442</v>
       </c>
       <c r="G148" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H148" s="1">
         <v>8</v>
@@ -13087,13 +13100,13 @@
         <v>239</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>27</v>
@@ -13102,7 +13115,7 @@
         <v>44441</v>
       </c>
       <c r="G149" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H149" s="1">
         <v>9</v>
@@ -13123,13 +13136,13 @@
         <v>238</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>22</v>
@@ -13138,7 +13151,7 @@
         <v>44440</v>
       </c>
       <c r="G150" s="28">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="H150" s="1">
         <v>8</v>
@@ -13159,7 +13172,7 @@
         <v>237</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>20</v>
@@ -13195,7 +13208,7 @@
         <v>236</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>20</v>
@@ -13231,16 +13244,16 @@
         <v>235</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F153" s="5">
         <v>44318</v>
@@ -13267,13 +13280,13 @@
         <v>234</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>21</v>
@@ -13303,13 +13316,13 @@
         <v>233</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>23</v>
@@ -13339,13 +13352,13 @@
         <v>232</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>27</v>
@@ -13375,13 +13388,13 @@
         <v>231</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>30</v>
@@ -13399,7 +13412,7 @@
         <v>34</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>37</v>
@@ -13411,22 +13424,22 @@
         <v>230</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F158" s="5">
         <v>44288</v>
       </c>
       <c r="G158" s="28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H158" s="1">
         <v>9</v>
@@ -13447,13 +13460,13 @@
         <v>229</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>23</v>
@@ -13462,7 +13475,7 @@
         <v>44287</v>
       </c>
       <c r="G159" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H159" s="1">
         <v>8</v>
@@ -13483,22 +13496,22 @@
         <v>228</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F160" s="5">
         <v>44197</v>
       </c>
       <c r="G160" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H160" s="1">
         <v>10</v>
@@ -13519,16 +13532,16 @@
         <v>227</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F161" s="5">
         <v>44166</v>
@@ -13555,13 +13568,13 @@
         <v>226</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>30</v>
@@ -13591,13 +13604,13 @@
         <v>225</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>27</v>
@@ -13627,13 +13640,13 @@
         <v>224</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>23</v>
@@ -13642,7 +13655,7 @@
         <v>44112</v>
       </c>
       <c r="G164" s="28">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H164" s="1">
         <v>10</v>
@@ -13663,13 +13676,13 @@
         <v>223</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>23</v>
@@ -13678,7 +13691,7 @@
         <v>44111</v>
       </c>
       <c r="G165" s="28">
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="H165" s="1">
         <v>8</v>
@@ -13699,22 +13712,22 @@
         <v>222</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F166" s="5">
         <v>44110</v>
       </c>
       <c r="G166" s="28">
-        <v>0</v>
+        <v>3.5416666666666665</v>
       </c>
       <c r="H166" s="1">
         <v>8</v>
@@ -13735,16 +13748,16 @@
         <v>221</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F167" s="5">
         <v>44109</v>
@@ -13759,7 +13772,7 @@
         <v>33</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>37</v>
@@ -13771,13 +13784,13 @@
         <v>220</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>65</v>
@@ -13795,7 +13808,7 @@
         <v>34</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K168" s="1" t="s">
         <v>37</v>
@@ -13807,13 +13820,13 @@
         <v>219</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>23</v>
@@ -13843,13 +13856,13 @@
         <v>218</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>23</v>
@@ -13879,13 +13892,13 @@
         <v>217</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>65</v>
@@ -13915,13 +13928,13 @@
         <v>216</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>23</v>
@@ -13951,13 +13964,13 @@
         <v>215</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>21</v>
@@ -13966,7 +13979,7 @@
         <v>44044</v>
       </c>
       <c r="G173" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H173" s="1">
         <v>9</v>
@@ -13987,13 +14000,13 @@
         <v>214</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>24</v>
@@ -14023,13 +14036,13 @@
         <v>213</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>21</v>
@@ -14059,16 +14072,16 @@
         <v>212</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F176" s="5">
         <v>44013</v>
@@ -14083,7 +14096,7 @@
         <v>32</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K176" s="1" t="s">
         <v>37</v>
@@ -14095,13 +14108,13 @@
         <v>211</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>22</v>
@@ -14131,13 +14144,13 @@
         <v>210</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>30</v>
@@ -14167,13 +14180,13 @@
         <v>209</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>24</v>
@@ -14203,13 +14216,13 @@
         <v>208</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>22</v>
@@ -14239,13 +14252,13 @@
         <v>207</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>25</v>
@@ -14275,16 +14288,16 @@
         <v>206</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F182" s="5">
         <v>43955</v>
@@ -14311,13 +14324,13 @@
         <v>205</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>21</v>
@@ -14347,13 +14360,13 @@
         <v>204</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>24</v>
@@ -14383,13 +14396,13 @@
         <v>203</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>22</v>
@@ -14419,13 +14432,13 @@
         <v>202</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>65</v>
@@ -14455,13 +14468,13 @@
         <v>201</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>30</v>
@@ -14491,13 +14504,13 @@
         <v>200</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>65</v>
@@ -14506,7 +14519,7 @@
         <v>43922</v>
       </c>
       <c r="G188" s="28">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="H188" s="1">
         <v>9</v>
@@ -14527,13 +14540,13 @@
         <v>199</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>24</v>
@@ -14542,7 +14555,7 @@
         <v>43891</v>
       </c>
       <c r="G189" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H189" s="1">
         <v>10</v>
@@ -14563,13 +14576,13 @@
         <v>198</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>23</v>
@@ -14599,13 +14612,13 @@
         <v>197</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>30</v>
@@ -14614,7 +14627,7 @@
         <v>43711</v>
       </c>
       <c r="G191" s="28">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="H191" s="1">
         <v>6</v>
@@ -14635,13 +14648,13 @@
         <v>196</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>30</v>
@@ -14650,7 +14663,7 @@
         <v>43710</v>
       </c>
       <c r="G192" s="28">
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="H192" s="1">
         <v>9</v>
@@ -14671,16 +14684,16 @@
         <v>195</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F193" s="5">
         <v>43709</v>
@@ -14695,7 +14708,7 @@
         <v>33</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K193" s="1" t="s">
         <v>37</v>
@@ -14707,13 +14720,13 @@
         <v>194</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>24</v>
@@ -14743,13 +14756,13 @@
         <v>193</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>21</v>
@@ -14758,7 +14771,7 @@
         <v>43617</v>
       </c>
       <c r="G195" s="28">
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="H195" s="1">
         <v>7</v>
@@ -14779,13 +14792,13 @@
         <v>192</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>21</v>
@@ -14815,16 +14828,16 @@
         <v>191</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F197" s="5">
         <v>43556</v>
@@ -14851,13 +14864,13 @@
         <v>190</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>23</v>
@@ -14866,7 +14879,7 @@
         <v>43525</v>
       </c>
       <c r="G198" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H198" s="1">
         <v>10</v>
@@ -14887,13 +14900,13 @@
         <v>189</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>23</v>
@@ -14923,13 +14936,13 @@
         <v>188</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>23</v>
@@ -14938,7 +14951,7 @@
         <v>43475</v>
       </c>
       <c r="G200" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200" s="1">
         <v>9</v>
@@ -14959,13 +14972,13 @@
         <v>187</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>23</v>
@@ -14974,7 +14987,7 @@
         <v>43474</v>
       </c>
       <c r="G201" s="28">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H201" s="1">
         <v>8</v>
@@ -14995,13 +15008,13 @@
         <v>186</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>23</v>
@@ -15031,22 +15044,22 @@
         <v>185</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F203" s="5">
         <v>43472</v>
       </c>
       <c r="G203" s="28">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="H203" s="1">
         <v>6</v>
@@ -15067,13 +15080,13 @@
         <v>184</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>23</v>
@@ -15082,7 +15095,7 @@
         <v>43471</v>
       </c>
       <c r="G204" s="28">
-        <v>0</v>
+        <v>1.0416666666666667</v>
       </c>
       <c r="H204" s="1">
         <v>8</v>
@@ -15103,22 +15116,22 @@
         <v>183</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F205" s="5">
         <v>43470</v>
       </c>
       <c r="G205" s="28">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="H205" s="1">
         <v>8</v>
@@ -15139,13 +15152,13 @@
         <v>182</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>21</v>
@@ -15175,13 +15188,13 @@
         <v>181</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>23</v>
@@ -15211,13 +15224,13 @@
         <v>180</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>23</v>
@@ -15247,13 +15260,13 @@
         <v>179</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>21</v>
@@ -15262,7 +15275,7 @@
         <v>43466</v>
       </c>
       <c r="G209" s="28">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H209" s="1">
         <v>7</v>
@@ -15283,13 +15296,13 @@
         <v>178</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>23</v>
@@ -15298,7 +15311,7 @@
         <v>43445</v>
       </c>
       <c r="G210" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H210" s="1">
         <v>10</v>
@@ -15319,13 +15332,13 @@
         <v>177</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>23</v>
@@ -15334,7 +15347,7 @@
         <v>43444</v>
       </c>
       <c r="G211" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H211" s="1">
         <v>10</v>
@@ -15355,13 +15368,13 @@
         <v>176</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>23</v>
@@ -15391,13 +15404,13 @@
         <v>175</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>23</v>
@@ -15406,7 +15419,7 @@
         <v>43442</v>
       </c>
       <c r="G213" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H213" s="1">
         <v>10</v>
@@ -15427,13 +15440,13 @@
         <v>174</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>23</v>
@@ -15442,7 +15455,7 @@
         <v>43441</v>
       </c>
       <c r="G214" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H214" s="1">
         <v>10</v>
@@ -15463,13 +15476,13 @@
         <v>173</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>23</v>
@@ -15499,13 +15512,13 @@
         <v>172</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>21</v>
@@ -15514,7 +15527,7 @@
         <v>43439</v>
       </c>
       <c r="G216" s="28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H216" s="1">
         <v>10</v>
@@ -15535,13 +15548,13 @@
         <v>171</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>23</v>
@@ -15571,13 +15584,13 @@
         <v>170</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>23</v>
@@ -15607,13 +15620,13 @@
         <v>169</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>23</v>
@@ -15622,7 +15635,7 @@
         <v>43436</v>
       </c>
       <c r="G219" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H219" s="1">
         <v>11</v>
@@ -15643,13 +15656,13 @@
         <v>168</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>23</v>
@@ -15679,13 +15692,13 @@
         <v>167</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>23</v>
@@ -15715,16 +15728,16 @@
         <v>166</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F222" s="5">
         <v>43406</v>
@@ -15751,13 +15764,13 @@
         <v>165</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>23</v>
@@ -15787,13 +15800,13 @@
         <v>164</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>23</v>
@@ -15823,13 +15836,13 @@
         <v>163</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>23</v>
@@ -15838,7 +15851,7 @@
         <v>43348</v>
       </c>
       <c r="G225" s="28">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="H225" s="1">
         <v>8</v>
@@ -15859,13 +15872,13 @@
         <v>162</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>23</v>
@@ -15895,13 +15908,13 @@
         <v>161</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>23</v>
@@ -15931,13 +15944,13 @@
         <v>160</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>23</v>
@@ -15967,13 +15980,13 @@
         <v>159</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>23</v>
@@ -16003,13 +16016,13 @@
         <v>158</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>23</v>
@@ -16039,13 +16052,13 @@
         <v>157</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>23</v>
@@ -16075,13 +16088,13 @@
         <v>156</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>22</v>
@@ -16090,7 +16103,7 @@
         <v>43315</v>
       </c>
       <c r="G232" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H232" s="1">
         <v>11</v>
@@ -16111,13 +16124,13 @@
         <v>155</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>21</v>
@@ -16126,7 +16139,7 @@
         <v>43314</v>
       </c>
       <c r="G233" s="28">
-        <v>0</v>
+        <v>1.0625</v>
       </c>
       <c r="H233" s="1">
         <v>9</v>
@@ -16147,13 +16160,13 @@
         <v>154</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>22</v>
@@ -16183,13 +16196,13 @@
         <v>153</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>22</v>
@@ -16219,13 +16232,13 @@
         <v>152</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>23</v>
@@ -16255,13 +16268,13 @@
         <v>151</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>23</v>
@@ -16291,13 +16304,13 @@
         <v>150</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>23</v>
@@ -16306,7 +16319,7 @@
         <v>43282</v>
       </c>
       <c r="G238" s="28">
-        <v>0</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H238" s="1">
         <v>7</v>
@@ -16327,13 +16340,13 @@
         <v>149</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>22</v>
@@ -16363,13 +16376,13 @@
         <v>148</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>23</v>
@@ -16399,13 +16412,13 @@
         <v>147</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>23</v>
@@ -16435,13 +16448,13 @@
         <v>146</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>23</v>
@@ -16471,13 +16484,13 @@
         <v>145</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>27</v>
@@ -16486,7 +16499,7 @@
         <v>43223</v>
       </c>
       <c r="G243" s="28">
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="H243" s="1">
         <v>1</v>
@@ -16507,16 +16520,16 @@
         <v>144</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F244" s="5">
         <v>43222</v>
@@ -16543,13 +16556,13 @@
         <v>143</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>21</v>
@@ -16558,7 +16571,7 @@
         <v>43221</v>
       </c>
       <c r="G245" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H245" s="1">
         <v>10</v>
@@ -16579,13 +16592,13 @@
         <v>142</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>23</v>
@@ -16615,13 +16628,13 @@
         <v>141</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>23</v>
@@ -16651,13 +16664,13 @@
         <v>140</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>23</v>
@@ -16666,7 +16679,7 @@
         <v>43191</v>
       </c>
       <c r="G248" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H248" s="1">
         <v>7</v>
@@ -16687,13 +16700,13 @@
         <v>139</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>28</v>
@@ -16702,7 +16715,7 @@
         <v>43161</v>
       </c>
       <c r="G249" s="28">
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="H249" s="1">
         <v>7</v>
@@ -16723,13 +16736,13 @@
         <v>138</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>23</v>
@@ -16759,13 +16772,13 @@
         <v>137</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>23</v>
@@ -16795,13 +16808,13 @@
         <v>136</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>23</v>
@@ -16831,13 +16844,13 @@
         <v>135</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>22</v>
@@ -16846,7 +16859,7 @@
         <v>43133</v>
       </c>
       <c r="G253" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H253" s="1">
         <v>10</v>
@@ -16867,13 +16880,13 @@
         <v>134</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>21</v>
@@ -16882,7 +16895,7 @@
         <v>43132</v>
       </c>
       <c r="G254" s="28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H254" s="1">
         <v>6</v>
@@ -16903,13 +16916,13 @@
         <v>133</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>21</v>
@@ -16918,7 +16931,7 @@
         <v>43105</v>
       </c>
       <c r="G255" s="28">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H255" s="1">
         <v>6</v>
@@ -16939,13 +16952,13 @@
         <v>132</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>30</v>
@@ -16954,7 +16967,7 @@
         <v>43104</v>
       </c>
       <c r="G256" s="28">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="H256" s="1">
         <v>7</v>
@@ -16975,13 +16988,13 @@
         <v>131</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>30</v>
@@ -16990,7 +17003,7 @@
         <v>43103</v>
       </c>
       <c r="G257" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H257" s="1">
         <v>8</v>
@@ -17011,13 +17024,13 @@
         <v>130</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>22</v>
@@ -17026,7 +17039,7 @@
         <v>43102</v>
       </c>
       <c r="G258" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H258" s="1">
         <v>7</v>
@@ -17047,16 +17060,16 @@
         <v>129</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F259" s="5">
         <v>43101</v>
@@ -17071,7 +17084,7 @@
         <v>32</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K259" s="1" t="s">
         <v>37</v>
@@ -17083,13 +17096,13 @@
         <v>128</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>65</v>
@@ -17098,7 +17111,7 @@
         <v>43071</v>
       </c>
       <c r="G260" s="28">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H260" s="1">
         <v>7</v>
@@ -17119,13 +17132,13 @@
         <v>127</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>27</v>
@@ -17155,7 +17168,7 @@
         <v>126</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>20</v>
@@ -17170,7 +17183,7 @@
         <v>43048</v>
       </c>
       <c r="G262" s="28">
-        <v>0</v>
+        <v>2.7083333333333335</v>
       </c>
       <c r="H262" s="1">
         <v>6</v>
@@ -17179,7 +17192,7 @@
         <v>33</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K262" s="1" t="s">
         <v>37</v>
@@ -17191,13 +17204,13 @@
         <v>125</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>23</v>
@@ -17206,7 +17219,7 @@
         <v>43047</v>
       </c>
       <c r="G263" s="28">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="H263" s="1">
         <v>7</v>
@@ -17227,13 +17240,13 @@
         <v>124</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>27</v>
@@ -17242,7 +17255,7 @@
         <v>43046</v>
       </c>
       <c r="G264" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H264" s="1">
         <v>10</v>
@@ -17263,13 +17276,13 @@
         <v>123</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>27</v>
@@ -17278,7 +17291,7 @@
         <v>43045</v>
       </c>
       <c r="G265" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H265" s="1">
         <v>9</v>
@@ -17299,13 +17312,13 @@
         <v>122</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>21</v>
@@ -17335,13 +17348,13 @@
         <v>121</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>21</v>
@@ -17371,13 +17384,13 @@
         <v>120</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>21</v>
@@ -17407,13 +17420,13 @@
         <v>119</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>95</v>
+        <v>511</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>27</v>
@@ -17422,7 +17435,7 @@
         <v>43041</v>
       </c>
       <c r="G269" s="28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H269" s="1">
         <v>8</v>
@@ -17443,13 +17456,13 @@
         <v>118</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>24</v>
@@ -17479,13 +17492,13 @@
         <v>117</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>23</v>
@@ -17494,7 +17507,7 @@
         <v>43013</v>
       </c>
       <c r="G271" s="28">
-        <v>0</v>
+        <v>1.0416666666666667</v>
       </c>
       <c r="H271" s="1">
         <v>7</v>
@@ -17515,13 +17528,13 @@
         <v>116</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>27</v>
@@ -17551,13 +17564,13 @@
         <v>115</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>23</v>
@@ -17587,13 +17600,13 @@
         <v>114</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>24</v>
@@ -17623,13 +17636,13 @@
         <v>113</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>22</v>
@@ -17659,13 +17672,13 @@
         <v>112</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>23</v>
@@ -17674,7 +17687,7 @@
         <v>42983</v>
       </c>
       <c r="G276" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H276" s="1">
         <v>7</v>
@@ -17695,13 +17708,13 @@
         <v>111</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>23</v>
@@ -17710,7 +17723,7 @@
         <v>42982</v>
       </c>
       <c r="G277" s="28">
-        <v>0</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="H277" s="1">
         <v>8</v>
@@ -17731,13 +17744,13 @@
         <v>110</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>28</v>
@@ -17767,13 +17780,13 @@
         <v>109</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>23</v>
@@ -17782,7 +17795,7 @@
         <v>42980</v>
       </c>
       <c r="G279" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H279" s="1">
         <v>7</v>
@@ -17803,22 +17816,22 @@
         <v>108</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F280" s="5">
         <v>42979</v>
       </c>
       <c r="G280" s="28">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="H280" s="1">
         <v>8</v>
@@ -17839,13 +17852,13 @@
         <v>107</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>23</v>
@@ -17875,13 +17888,13 @@
         <v>106</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>23</v>
@@ -17890,7 +17903,7 @@
         <v>42951</v>
       </c>
       <c r="G282" s="28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H282" s="1">
         <v>8</v>
@@ -17911,13 +17924,13 @@
         <v>105</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>28</v>
@@ -17926,7 +17939,7 @@
         <v>42950</v>
       </c>
       <c r="G283" s="28">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H283" s="1">
         <v>7</v>
@@ -17947,13 +17960,13 @@
         <v>104</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>23</v>
@@ -17983,13 +17996,13 @@
         <v>103</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>21</v>
@@ -17998,7 +18011,7 @@
         <v>42948</v>
       </c>
       <c r="G285" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H285" s="1">
         <v>10</v>
@@ -18019,13 +18032,13 @@
         <v>102</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>76</v>
+        <v>512</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>65</v>
@@ -18034,7 +18047,7 @@
         <v>42921</v>
       </c>
       <c r="G286" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H286" s="1">
         <v>6</v>
@@ -18058,10 +18071,10 @@
         <v>75</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>24</v>
@@ -18091,13 +18104,13 @@
         <v>100</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>24</v>
@@ -18130,10 +18143,10 @@
         <v>74</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>24</v>
@@ -18166,10 +18179,10 @@
         <v>73</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>23</v>
@@ -18202,10 +18215,10 @@
         <v>72</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>23</v>
@@ -18214,7 +18227,7 @@
         <v>42887</v>
       </c>
       <c r="G291" s="28">
-        <v>0</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="H291" s="1">
         <v>10</v>
@@ -18238,10 +18251,10 @@
         <v>68</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>23</v>
@@ -18274,10 +18287,10 @@
         <v>67</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>30</v>
@@ -18286,7 +18299,7 @@
         <v>42829</v>
       </c>
       <c r="G293" s="28">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H293" s="1">
         <v>7</v>
@@ -18307,13 +18320,13 @@
         <v>94</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C294" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>22</v>
@@ -18322,7 +18335,7 @@
         <v>42828</v>
       </c>
       <c r="G294" s="28">
-        <v>0</v>
+        <v>1.0416666666666667</v>
       </c>
       <c r="H294" s="1">
         <v>10</v>
@@ -18343,13 +18356,13 @@
         <v>93</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>22</v>
@@ -18358,7 +18371,7 @@
         <v>42827</v>
       </c>
       <c r="G295" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H295" s="1">
         <v>9</v>
@@ -18379,13 +18392,13 @@
         <v>92</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>69</v>
@@ -18394,7 +18407,7 @@
         <v>42826</v>
       </c>
       <c r="G296" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H296" s="1">
         <v>8</v>
@@ -18415,13 +18428,13 @@
         <v>91</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>22</v>
@@ -18454,10 +18467,10 @@
         <v>64</v>
       </c>
       <c r="C298" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>23</v>
@@ -18466,7 +18479,7 @@
         <v>42797</v>
       </c>
       <c r="G298" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H298" s="1">
         <v>10</v>
@@ -18490,10 +18503,10 @@
         <v>63</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>65</v>
@@ -18502,7 +18515,7 @@
         <v>42796</v>
       </c>
       <c r="G299" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H299" s="1">
         <v>9</v>
@@ -18526,10 +18539,10 @@
         <v>62</v>
       </c>
       <c r="C300" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>22</v>
@@ -18538,7 +18551,7 @@
         <v>42795</v>
       </c>
       <c r="G300" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H300" s="1">
         <v>10</v>
@@ -18562,10 +18575,10 @@
         <v>61</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>21</v>
@@ -18574,7 +18587,7 @@
         <v>42770</v>
       </c>
       <c r="G301" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H301" s="1">
         <v>8</v>
@@ -18598,10 +18611,10 @@
         <v>60</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>21</v>
@@ -18610,7 +18623,7 @@
         <v>42769</v>
       </c>
       <c r="G302" s="28">
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="H302" s="1">
         <v>7</v>
@@ -18634,10 +18647,10 @@
         <v>58</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>21</v>
@@ -18667,13 +18680,13 @@
         <v>84</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>27</v>
@@ -18706,10 +18719,10 @@
         <v>57</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>23</v>
@@ -18718,7 +18731,7 @@
         <v>42740</v>
       </c>
       <c r="G305" s="28">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H305" s="1">
         <v>11</v>
@@ -18742,10 +18755,10 @@
         <v>56</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>21</v>
@@ -18775,13 +18788,13 @@
         <v>81</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>21</v>
@@ -18814,10 +18827,10 @@
         <v>55</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>28</v>
@@ -18850,10 +18863,10 @@
         <v>54</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>27</v>
@@ -18862,7 +18875,7 @@
         <v>42736</v>
       </c>
       <c r="G309" s="28">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H309" s="1">
         <v>9</v>
@@ -18898,7 +18911,7 @@
         <v>42676</v>
       </c>
       <c r="G310" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H310" s="1">
         <v>5</v>
@@ -18922,10 +18935,10 @@
         <v>18</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>23</v>
@@ -18934,7 +18947,7 @@
         <v>42675</v>
       </c>
       <c r="G311" s="28">
-        <v>0</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="H311" s="1">
         <v>5</v>
@@ -18955,13 +18968,13 @@
         <v>76</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>22</v>
@@ -18970,7 +18983,7 @@
         <v>42646</v>
       </c>
       <c r="G312" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" s="1">
         <v>8</v>
@@ -18991,13 +19004,13 @@
         <v>75</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>21</v>
@@ -19006,7 +19019,7 @@
         <v>42645</v>
       </c>
       <c r="G313" s="28">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="H313" s="1">
         <v>7</v>
@@ -19027,7 +19040,7 @@
         <v>74</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>20</v>
@@ -19042,7 +19055,7 @@
         <v>42644</v>
       </c>
       <c r="G314" s="28">
-        <v>0</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="H314" s="1">
         <v>6</v>
@@ -19051,7 +19064,7 @@
         <v>33</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K314" s="1" t="s">
         <v>37</v>
@@ -19063,13 +19076,13 @@
         <v>73</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>23</v>
@@ -19078,7 +19091,7 @@
         <v>42617</v>
       </c>
       <c r="G315" s="28">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="H315" s="1">
         <v>7</v>
@@ -19102,10 +19115,10 @@
         <v>17</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>29</v>
@@ -19114,7 +19127,7 @@
         <v>42616</v>
       </c>
       <c r="G316" s="28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H316" s="1">
         <v>7</v>
@@ -19138,10 +19151,10 @@
         <v>16</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>28</v>
@@ -19150,7 +19163,7 @@
         <v>42615</v>
       </c>
       <c r="G317" s="28">
-        <v>0</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="H317" s="1">
         <v>8</v>
@@ -19174,10 +19187,10 @@
         <v>15</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>27</v>
@@ -19186,7 +19199,7 @@
         <v>42614</v>
       </c>
       <c r="G318" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H318" s="1">
         <v>8</v>
@@ -19210,10 +19223,10 @@
         <v>14</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>23</v>
@@ -19222,7 +19235,7 @@
         <v>42583</v>
       </c>
       <c r="G319" s="28">
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="H319" s="1">
         <v>9</v>
@@ -19246,10 +19259,10 @@
         <v>13</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>23</v>
@@ -19258,7 +19271,7 @@
         <v>42552</v>
       </c>
       <c r="G320" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H320" s="1">
         <v>8</v>
@@ -19294,7 +19307,7 @@
         <v>42461</v>
       </c>
       <c r="G321" s="28">
-        <v>0</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="H321" s="1">
         <v>8</v>
@@ -19351,7 +19364,7 @@
         <v>65</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>20</v>
@@ -19423,7 +19436,7 @@
         <v>63</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>20</v>
@@ -19459,7 +19472,7 @@
         <v>62</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>20</v>
@@ -19498,10 +19511,10 @@
         <v>8</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>23</v>
@@ -19510,7 +19523,7 @@
         <v>42372</v>
       </c>
       <c r="G327" s="28">
-        <v>0</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="H327" s="1">
         <v>9</v>
@@ -19534,10 +19547,10 @@
         <v>7</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>23</v>
@@ -19546,7 +19559,7 @@
         <v>42371</v>
       </c>
       <c r="G328" s="28">
-        <v>0</v>
+        <v>1.1041666666666667</v>
       </c>
       <c r="H328" s="1">
         <v>9</v>
@@ -19570,10 +19583,10 @@
         <v>6</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>24</v>
@@ -19582,7 +19595,7 @@
         <v>42370</v>
       </c>
       <c r="G329" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H329" s="1">
         <v>11</v>
@@ -19603,13 +19616,13 @@
         <v>58</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>27</v>
@@ -19639,13 +19652,13 @@
         <v>57</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>65</v>
@@ -19675,13 +19688,13 @@
         <v>56</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>29</v>
@@ -19699,7 +19712,7 @@
         <v>52</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K332" s="1" t="s">
         <v>37</v>
@@ -19711,13 +19724,13 @@
         <v>55</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>29</v>
@@ -19735,7 +19748,7 @@
         <v>32</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K333" s="1" t="s">
         <v>37</v>
@@ -19747,13 +19760,13 @@
         <v>54</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>23</v>
@@ -19762,7 +19775,7 @@
         <v>42123</v>
       </c>
       <c r="G334" s="28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H334" s="1">
         <v>7</v>
@@ -19783,13 +19796,13 @@
         <v>53</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>65</v>
@@ -19798,7 +19811,7 @@
         <v>42123</v>
       </c>
       <c r="G335" s="28">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="H335" s="1">
         <v>7</v>
@@ -19807,7 +19820,7 @@
         <v>34</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K335" s="1" t="s">
         <v>37</v>
@@ -19819,13 +19832,13 @@
         <v>52</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>21</v>
@@ -19834,7 +19847,7 @@
         <v>42121</v>
       </c>
       <c r="G336" s="28">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="H336" s="1">
         <v>5</v>
@@ -19855,22 +19868,22 @@
         <v>51</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F337" s="5">
         <v>42121</v>
       </c>
       <c r="G337" s="28">
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="H337" s="1">
         <v>7</v>
@@ -19879,7 +19892,7 @@
         <v>34</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K337" s="1" t="s">
         <v>37</v>
@@ -19891,13 +19904,13 @@
         <v>50</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>27</v>
@@ -19906,7 +19919,7 @@
         <v>42120</v>
       </c>
       <c r="G338" s="28">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="H338" s="1">
         <v>5</v>
@@ -19927,13 +19940,13 @@
         <v>49</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>27</v>
@@ -19942,7 +19955,7 @@
         <v>42119</v>
       </c>
       <c r="G339" s="28">
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H339" s="1">
         <v>5</v>
@@ -19963,13 +19976,13 @@
         <v>48</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>27</v>
@@ -19978,7 +19991,7 @@
         <v>42119</v>
       </c>
       <c r="G340" s="28">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H340" s="1">
         <v>4</v>
@@ -19999,13 +20012,13 @@
         <v>47</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>27</v>
@@ -20014,7 +20027,7 @@
         <v>42118</v>
       </c>
       <c r="G341" s="28">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H341" s="1">
         <v>3</v>
@@ -20035,13 +20048,13 @@
         <v>46</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>27</v>
@@ -20050,7 +20063,7 @@
         <v>42116</v>
       </c>
       <c r="G342" s="28">
-        <v>0</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="H342" s="1">
         <v>5</v>
@@ -20071,13 +20084,13 @@
         <v>45</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>27</v>
@@ -20086,7 +20099,7 @@
         <v>42114</v>
       </c>
       <c r="G343" s="28">
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="H343" s="1">
         <v>4</v>
@@ -20107,13 +20120,13 @@
         <v>44</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>21</v>
@@ -20122,7 +20135,7 @@
         <v>42114</v>
       </c>
       <c r="G344" s="28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H344" s="1">
         <v>5</v>
@@ -20143,13 +20156,13 @@
         <v>43</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>27</v>
@@ -20158,7 +20171,7 @@
         <v>42112</v>
       </c>
       <c r="G345" s="28">
-        <v>0</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="H345" s="1">
         <v>5</v>
@@ -20179,13 +20192,13 @@
         <v>42</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>27</v>
@@ -20194,7 +20207,7 @@
         <v>42112</v>
       </c>
       <c r="G346" s="28">
-        <v>0</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="H346" s="1">
         <v>5</v>
@@ -20215,13 +20228,13 @@
         <v>41</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>65</v>
@@ -20230,7 +20243,7 @@
         <v>42108</v>
       </c>
       <c r="G347" s="28">
-        <v>0</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="H347" s="1">
         <v>7</v>
@@ -20251,13 +20264,13 @@
         <v>40</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>22</v>
@@ -20266,7 +20279,7 @@
         <v>42108</v>
       </c>
       <c r="G348" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H348" s="1">
         <v>7</v>
@@ -20287,13 +20300,13 @@
         <v>39</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>27</v>
@@ -20302,7 +20315,7 @@
         <v>42105</v>
       </c>
       <c r="G349" s="28">
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H349" s="1">
         <v>6</v>
@@ -20323,13 +20336,13 @@
         <v>38</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>28</v>
@@ -20338,7 +20351,7 @@
         <v>42102</v>
       </c>
       <c r="G350" s="28">
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="H350" s="1">
         <v>5</v>
@@ -20359,13 +20372,13 @@
         <v>37</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>30</v>
@@ -20374,7 +20387,7 @@
         <v>42099</v>
       </c>
       <c r="G351" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H351" s="1">
         <v>9</v>
@@ -20395,13 +20408,13 @@
         <v>36</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>27</v>
@@ -20410,7 +20423,7 @@
         <v>42099</v>
       </c>
       <c r="G352" s="28">
-        <v>0</v>
+        <v>0.14583333333333334</v>
       </c>
       <c r="H352" s="1">
         <v>5</v>
@@ -20431,13 +20444,13 @@
         <v>35</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>65</v>
@@ -20446,7 +20459,7 @@
         <v>42099</v>
       </c>
       <c r="G353" s="28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H353" s="1">
         <v>6</v>
@@ -20467,13 +20480,13 @@
         <v>34</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>22</v>
@@ -20482,7 +20495,7 @@
         <v>42092</v>
       </c>
       <c r="G354" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H354" s="1">
         <v>9</v>
@@ -20503,13 +20516,13 @@
         <v>33</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>30</v>
@@ -20518,7 +20531,7 @@
         <v>42091</v>
       </c>
       <c r="G355" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H355" s="1">
         <v>7</v>
@@ -20527,7 +20540,7 @@
         <v>32</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K355" s="1" t="s">
         <v>37</v>
@@ -20539,13 +20552,13 @@
         <v>32</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>22</v>
@@ -20554,7 +20567,7 @@
         <v>42087</v>
       </c>
       <c r="G356" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H356" s="1">
         <v>7</v>
@@ -20575,13 +20588,13 @@
         <v>31</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>22</v>
@@ -20590,7 +20603,7 @@
         <v>42085</v>
       </c>
       <c r="G357" s="28">
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H357" s="1">
         <v>7</v>
@@ -20611,13 +20624,13 @@
         <v>30</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>22</v>
@@ -20626,7 +20639,7 @@
         <v>42078</v>
       </c>
       <c r="G358" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H358" s="1">
         <v>8</v>
@@ -20647,13 +20660,13 @@
         <v>29</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>22</v>
@@ -20683,13 +20696,13 @@
         <v>28</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>28</v>
@@ -20698,7 +20711,7 @@
         <v>42068</v>
       </c>
       <c r="G360" s="28">
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="H360" s="1">
         <v>5</v>
@@ -20719,13 +20732,13 @@
         <v>27</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>22</v>
@@ -20734,7 +20747,7 @@
         <v>42066</v>
       </c>
       <c r="G361" s="28">
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="H361" s="1">
         <v>8</v>
@@ -20755,13 +20768,13 @@
         <v>26</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>21</v>
@@ -20770,7 +20783,7 @@
         <v>42064</v>
       </c>
       <c r="G362" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H362" s="1">
         <v>6</v>
@@ -20791,13 +20804,13 @@
         <v>25</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>30</v>
@@ -20806,7 +20819,7 @@
         <v>42063</v>
       </c>
       <c r="G363" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H363" s="1">
         <v>7</v>
@@ -20815,7 +20828,7 @@
         <v>32</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K363" s="1" t="s">
         <v>37</v>
@@ -20827,13 +20840,13 @@
         <v>24</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>27</v>
@@ -20863,13 +20876,13 @@
         <v>23</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>27</v>
@@ -20899,13 +20912,13 @@
         <v>22</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>27</v>
@@ -20914,7 +20927,7 @@
         <v>42045</v>
       </c>
       <c r="G366" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H366" s="1">
         <v>6</v>
@@ -20935,13 +20948,13 @@
         <v>21</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>27</v>
@@ -20950,7 +20963,7 @@
         <v>42037</v>
       </c>
       <c r="G367" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H367" s="1">
         <v>7</v>
@@ -20971,13 +20984,13 @@
         <v>20</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>65</v>
@@ -21007,13 +21020,13 @@
         <v>19</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>27</v>
@@ -21022,7 +21035,7 @@
         <v>42024</v>
       </c>
       <c r="G369" s="28">
-        <v>0</v>
+        <v>1.3958333333333333</v>
       </c>
       <c r="H369" s="1">
         <v>7</v>
@@ -21043,13 +21056,13 @@
         <v>18</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>30</v>
@@ -21058,7 +21071,7 @@
         <v>42021</v>
       </c>
       <c r="G370" s="28">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="H370" s="1">
         <v>7</v>
@@ -21079,13 +21092,13 @@
         <v>17</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>22</v>
@@ -21115,16 +21128,16 @@
         <v>16</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F372" s="5">
         <v>42004</v>
@@ -21151,13 +21164,13 @@
         <v>15</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>23</v>
@@ -21187,13 +21200,13 @@
         <v>14</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>22</v>
@@ -21223,13 +21236,13 @@
         <v>13</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>30</v>
@@ -21259,13 +21272,13 @@
         <v>12</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>22</v>
@@ -21274,7 +21287,7 @@
         <v>41903</v>
       </c>
       <c r="G376" s="28">
-        <v>0</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="H376" s="1">
         <v>10</v>
@@ -21295,13 +21308,13 @@
         <v>11</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>23</v>
@@ -21310,7 +21323,7 @@
         <v>41893</v>
       </c>
       <c r="G377" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H377" s="1">
         <v>9</v>
@@ -21334,10 +21347,10 @@
         <v>26</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>22</v>
@@ -21346,7 +21359,7 @@
         <v>41895</v>
       </c>
       <c r="G378" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H378" s="1">
         <v>7</v>
@@ -21367,13 +21380,13 @@
         <v>9</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>25</v>
@@ -21382,7 +21395,7 @@
         <v>41869</v>
       </c>
       <c r="G379" s="28">
-        <v>0</v>
+        <v>1.4583333333333333</v>
       </c>
       <c r="H379" s="1">
         <v>10</v>
@@ -21403,13 +21416,13 @@
         <v>8</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>22</v>
@@ -21418,7 +21431,7 @@
         <v>41755</v>
       </c>
       <c r="G380" s="28">
-        <v>0</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="H380" s="1">
         <v>10</v>
@@ -21439,13 +21452,13 @@
         <v>7</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>65</v>
@@ -21454,7 +21467,7 @@
         <v>41747</v>
       </c>
       <c r="G381" s="28">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H381" s="1">
         <v>9</v>
@@ -21475,13 +21488,13 @@
         <v>6</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>22</v>
@@ -21490,7 +21503,7 @@
         <v>41723</v>
       </c>
       <c r="G382" s="28">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="H382" s="1">
         <v>8</v>
@@ -21511,13 +21524,13 @@
         <v>5</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>30</v>
@@ -21526,7 +21539,7 @@
         <v>41713</v>
       </c>
       <c r="G383" s="28">
-        <v>0</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="H383" s="1">
         <v>7</v>
@@ -21550,10 +21563,10 @@
         <v>9</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>25</v>
@@ -21562,7 +21575,7 @@
         <v>41743</v>
       </c>
       <c r="G384" s="28">
-        <v>0</v>
+        <v>1.5416666666666667</v>
       </c>
       <c r="H384" s="1">
         <v>10</v>
@@ -21583,13 +21596,13 @@
         <v>3</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>27</v>
@@ -21598,7 +21611,7 @@
         <v>41720</v>
       </c>
       <c r="G385" s="28">
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H385" s="1">
         <v>10</v>
@@ -21619,13 +21632,13 @@
         <v>2</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>29</v>
@@ -21634,7 +21647,7 @@
         <v>41720</v>
       </c>
       <c r="G386" s="28">
-        <v>0</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="H386" s="1">
         <v>7</v>
@@ -21643,7 +21656,7 @@
         <v>34</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K386" s="1" t="s">
         <v>37</v>
@@ -21655,13 +21668,13 @@
         <v>1</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>23</v>
@@ -21670,7 +21683,7 @@
         <v>41700</v>
       </c>
       <c r="G387" s="28">
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="H387" s="1">
         <v>10</v>
@@ -21717,22 +21730,22 @@
     <mergeCell ref="O51:P51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 C3:L1048576 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>OR(ISNUMBER(FIND("NES",C1)),    ISNUMBER(FIND("SNES",C1)),    ISNUMBER(FIND("N64",C1)),    ISNUMBER(FIND("GC",C1)),    ISNUMBER(FIND("Wii",C1)),    ISNUMBER(FIND("Wii U",C1)),    ISNUMBER(FIND("Switch",C1)),    ISNUMBER(FIND("Switch 2",C1)),    ISNUMBER(FIND("GB",C1)),    ISNUMBER(FIND("GBC",C1)),    ISNUMBER(FIND("GBA",C1)),    ISNUMBER(FIND("DS",C1)),    ISNUMBER(FIND("3DS",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 S26:T29 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 S26:T29">
     <cfRule type="expression" dxfId="23" priority="18">
       <formula>OR(ISNUMBER(FIND("X One",C1)),    ISNUMBER(FIND("X Series",C1)),    ISNUMBER(FIND("X 360",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="22" priority="17">
       <formula>OR(ISNUMBER(FIND("PS1",C1)),    ISNUMBER(FIND("PS2",C1)),    ISNUMBER(FIND("PS3",C1)),    ISNUMBER(FIND("PS4",C1)),    ISNUMBER(FIND("PSP",C1)),    ISNUMBER(FIND("Vita",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 S26:T29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 S26:T29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="21" priority="19">
       <formula>ISNUMBER(FIND("PC",C1))</formula>
     </cfRule>
@@ -21740,7 +21753,7 @@
       <formula>ISNUMBER(FIND("MD",C1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M14 H1:H1048576">
+  <conditionalFormatting sqref="H1:H1048576 M4:M14">
     <cfRule type="expression" dxfId="19" priority="11">
       <formula>OR(ISNUMBER(FIND("11",H1)),)</formula>
     </cfRule>
@@ -21762,7 +21775,7 @@
       <formula>NOT(ISERROR(SEARCH("Não",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M22 M24:M34 M37:M53 M58:M1048576 I1:I1048576">
+  <conditionalFormatting sqref="M1:M22 I1:I1048576 M24:M34 M37:M53 M58:M1048576">
     <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="Fácil">
       <formula>NOT(ISERROR(SEARCH("Fácil",I1)))</formula>
     </cfRule>
@@ -21839,59 +21852,59 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="84" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
       <c r="F2" s="84" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G2" s="84"/>
       <c r="H2" s="84"/>
       <c r="J2" s="84" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K2" s="84"/>
       <c r="L2" s="84"/>
       <c r="N2" s="84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="O2" s="84"/>
       <c r="P2" s="84"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>1</v>
@@ -21905,7 +21918,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F4" s="22">
         <v>1</v>
@@ -21914,7 +21927,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J4" s="22">
         <v>1</v>
@@ -21923,7 +21936,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N4" s="22">
         <v>1</v>
@@ -21932,7 +21945,7 @@
         <v>11</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -21943,7 +21956,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="22">
         <v>2</v>
@@ -21952,7 +21965,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J5" s="22">
         <v>2</v>
@@ -21961,7 +21974,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N5" s="22">
         <v>2</v>
@@ -21970,7 +21983,7 @@
         <v>10</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -21981,7 +21994,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F6" s="22">
         <v>3</v>
@@ -21990,7 +22003,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J6" s="22">
         <v>3</v>
@@ -21999,7 +22012,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N6" s="22">
         <v>3</v>
@@ -22008,7 +22021,7 @@
         <v>10</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22019,7 +22032,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F7" s="22">
         <v>4</v>
@@ -22028,7 +22041,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J7" s="22">
         <v>4</v>
@@ -22037,7 +22050,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N7" s="22">
         <v>4</v>
@@ -22046,7 +22059,7 @@
         <v>10</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22057,7 +22070,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F8" s="22">
         <v>5</v>
@@ -22066,7 +22079,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J8" s="22">
         <v>5</v>
@@ -22075,7 +22088,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N8" s="22">
         <v>5</v>
@@ -22084,7 +22097,7 @@
         <v>10</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22095,7 +22108,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F9" s="22">
         <v>6</v>
@@ -22104,7 +22117,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J9" s="22">
         <v>6</v>
@@ -22113,7 +22126,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N9" s="22">
         <v>6</v>
@@ -22122,7 +22135,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22133,7 +22146,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F10" s="22">
         <v>7</v>
@@ -22142,7 +22155,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J10" s="22">
         <v>7</v>
@@ -22151,7 +22164,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N10" s="22">
         <v>7</v>
@@ -22171,7 +22184,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F11" s="22">
         <v>8</v>
@@ -22180,7 +22193,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J11" s="22">
         <v>8</v>
@@ -22189,7 +22202,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N11" s="22">
         <v>8</v>
@@ -22198,7 +22211,7 @@
         <v>10</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22209,7 +22222,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F12" s="22">
         <v>9</v>
@@ -22218,7 +22231,7 @@
         <v>8</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J12" s="22">
         <v>9</v>
@@ -22227,7 +22240,7 @@
         <v>8</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N12" s="22">
         <v>9</v>
@@ -22236,7 +22249,7 @@
         <v>10</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22247,7 +22260,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F13" s="22">
         <v>10</v>
@@ -22256,7 +22269,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J13" s="22">
         <v>10</v>
@@ -22265,7 +22278,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N13" s="22">
         <v>10</v>
@@ -22274,7 +22287,7 @@
         <v>10</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22285,7 +22298,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F14" s="22">
         <v>11</v>
@@ -22294,7 +22307,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J14" s="22">
         <v>11</v>
@@ -22303,7 +22316,7 @@
         <v>7</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N14" s="22">
         <v>11</v>
@@ -22312,7 +22325,7 @@
         <v>10</v>
       </c>
       <c r="P14" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22323,7 +22336,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F15" s="22">
         <v>12</v>
@@ -22332,7 +22345,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J15" s="22">
         <v>12</v>
@@ -22341,7 +22354,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N15" s="22">
         <v>12</v>
@@ -22350,7 +22363,7 @@
         <v>9</v>
       </c>
       <c r="P15" s="27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22361,7 +22374,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F16" s="22">
         <v>13</v>
@@ -22370,7 +22383,7 @@
         <v>8</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J16" s="22">
         <v>13</v>
@@ -22379,7 +22392,7 @@
         <v>7</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N16" s="22">
         <v>13</v>
@@ -22388,7 +22401,7 @@
         <v>9</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22399,7 +22412,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F17" s="22">
         <v>14</v>
@@ -22408,7 +22421,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J17" s="22">
         <v>14</v>
@@ -22417,7 +22430,7 @@
         <v>7</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N17" s="22">
         <v>14</v>
@@ -22426,7 +22439,7 @@
         <v>9</v>
       </c>
       <c r="P17" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22437,7 +22450,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F18" s="22">
         <v>15</v>
@@ -22446,7 +22459,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J18" s="22">
         <v>15</v>
@@ -22455,7 +22468,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N18" s="22">
         <v>15</v>
@@ -22464,7 +22477,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22475,7 +22488,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F19" s="22">
         <v>16</v>
@@ -22484,7 +22497,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J19" s="22">
         <v>16</v>
@@ -22493,7 +22506,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N19" s="22">
         <v>16</v>
@@ -22502,7 +22515,7 @@
         <v>9</v>
       </c>
       <c r="P19" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22513,7 +22526,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F20" s="22">
         <v>17</v>
@@ -22522,7 +22535,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J20" s="22">
         <v>17</v>
@@ -22531,7 +22544,7 @@
         <v>6</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N20" s="22">
         <v>17</v>
@@ -22540,7 +22553,7 @@
         <v>9</v>
       </c>
       <c r="P20" s="27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22551,7 +22564,7 @@
         <v>7</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F21" s="22">
         <v>18</v>
@@ -22560,7 +22573,7 @@
         <v>6</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J21" s="22">
         <v>18</v>
@@ -22569,7 +22582,7 @@
         <v>6</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="N21" s="22">
         <v>18</v>
@@ -22578,7 +22591,7 @@
         <v>9</v>
       </c>
       <c r="P21" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22589,7 +22602,7 @@
         <v>7</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F22" s="22">
         <v>19</v>
@@ -22598,7 +22611,7 @@
         <v>6</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J22" s="22">
         <v>19</v>
@@ -22607,7 +22620,7 @@
         <v>6</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N22" s="22">
         <v>19</v>
@@ -22616,7 +22629,7 @@
         <v>9</v>
       </c>
       <c r="P22" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22627,7 +22640,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F23" s="22">
         <v>20</v>
@@ -22636,7 +22649,7 @@
         <v>6</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J23" s="22">
         <v>20</v>
@@ -22645,7 +22658,7 @@
         <v>6</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N23" s="22">
         <v>20</v>
@@ -22654,7 +22667,7 @@
         <v>9</v>
       </c>
       <c r="P23" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22665,7 +22678,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J24" s="22">
         <v>21</v>
@@ -22674,7 +22687,7 @@
         <v>6</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N24" s="22">
         <v>21</v>
@@ -22683,7 +22696,7 @@
         <v>8</v>
       </c>
       <c r="P24" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22694,7 +22707,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J25" s="22">
         <v>22</v>
@@ -22703,7 +22716,7 @@
         <v>5</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N25" s="22">
         <v>22</v>
@@ -22712,7 +22725,7 @@
         <v>8</v>
       </c>
       <c r="P25" s="24" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22723,7 +22736,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J26" s="22">
         <v>23</v>
@@ -22732,7 +22745,7 @@
         <v>4</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N26" s="22">
         <v>23</v>
@@ -22741,7 +22754,7 @@
         <v>8</v>
       </c>
       <c r="P26" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22752,7 +22765,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J27" s="22">
         <v>24</v>
@@ -22761,7 +22774,7 @@
         <v>4</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N27" s="22">
         <v>24</v>
@@ -22770,7 +22783,7 @@
         <v>8</v>
       </c>
       <c r="P27" s="24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22781,7 +22794,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N28" s="22">
         <v>25</v>
@@ -22790,7 +22803,7 @@
         <v>8</v>
       </c>
       <c r="P28" s="24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22801,7 +22814,7 @@
         <v>8</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22812,7 +22825,7 @@
         <v>8</v>
       </c>
       <c r="P30" s="24" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22823,7 +22836,7 @@
         <v>7</v>
       </c>
       <c r="P31" s="24" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22834,7 +22847,7 @@
         <v>7</v>
       </c>
       <c r="P32" s="24" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22845,7 +22858,7 @@
         <v>7</v>
       </c>
       <c r="P33" s="24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22856,7 +22869,7 @@
         <v>7</v>
       </c>
       <c r="P34" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22867,7 +22880,7 @@
         <v>6</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22878,7 +22891,7 @@
         <v>6</v>
       </c>
       <c r="P36" s="25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22889,7 +22902,7 @@
         <v>6</v>
       </c>
       <c r="P37" s="25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22900,7 +22913,7 @@
         <v>6</v>
       </c>
       <c r="P38" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/jogos/Lista de Jogos Finalizados.xlsx
+++ b/jogos/Lista de Jogos Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1DACB9-14A6-4331-AF6E-0541DD884B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855241B6-70CF-4C8F-B759-6B616FCDB7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{185F8663-3FF1-4EF9-AA90-43B25B82DF02}"/>
   </bookViews>
@@ -2956,7 +2956,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="515">
   <si>
     <t>Nº</t>
   </si>
@@ -5419,6 +5419,21 @@
   </si>
   <si>
     <t>Super Bomberman R</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Super Bomberman R - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>[P]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6901,7 +6916,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>343</v>
@@ -8255,7 +8270,7 @@
       </c>
       <c r="N25" s="42">
         <f>COUNTIFS(B:B,"*[P]*")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>359</v>
@@ -9008,7 +9023,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M39,1,1), $F:$F, "&lt;="&amp;DATE(M39,12,31))</f>
+        <f t="shared" ref="O39:O51" si="0">SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M39,1,1), $F:$F, "&lt;="&amp;DATE(M39,12,31))</f>
         <v>21.778043981481481</v>
       </c>
       <c r="P39" s="77"/>
@@ -9057,7 +9072,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M40,1,1), $F:$F, "&lt;="&amp;DATE(M40,12,31))</f>
+        <f t="shared" si="0"/>
         <v>39.712557870370361</v>
       </c>
       <c r="P40" s="79"/>
@@ -9106,7 +9121,7 @@
         <v>24</v>
       </c>
       <c r="O41" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M41,1,1), $F:$F, "&lt;="&amp;DATE(M41,12,31))</f>
+        <f t="shared" si="0"/>
         <v>15.460520833333334</v>
       </c>
       <c r="P41" s="77"/>
@@ -9155,7 +9170,7 @@
         <v>35</v>
       </c>
       <c r="O42" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M42,1,1), $F:$F, "&lt;="&amp;DATE(M42,12,31))</f>
+        <f t="shared" si="0"/>
         <v>66.78905092592592</v>
       </c>
       <c r="P42" s="79"/>
@@ -9203,7 +9218,7 @@
         <v>33</v>
       </c>
       <c r="O43" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M43,1,1), $F:$F, "&lt;="&amp;DATE(M43,12,31))</f>
+        <f t="shared" si="0"/>
         <v>58.889837962962957</v>
       </c>
       <c r="P43" s="77"/>
@@ -9251,7 +9266,7 @@
         <v>20</v>
       </c>
       <c r="O44" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M44,1,1), $F:$F, "&lt;="&amp;DATE(M44,12,31))</f>
+        <f t="shared" si="0"/>
         <v>47.408263888888897</v>
       </c>
       <c r="P44" s="79"/>
@@ -9299,7 +9314,7 @@
         <v>29</v>
       </c>
       <c r="O45" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M45,1,1), $F:$F, "&lt;="&amp;DATE(M45,12,31))</f>
+        <f t="shared" si="0"/>
         <v>63.090277777777764</v>
       </c>
       <c r="P45" s="77"/>
@@ -9347,7 +9362,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M46,1,1), $F:$F, "&lt;="&amp;DATE(M46,12,31))</f>
+        <f t="shared" si="0"/>
         <v>57.896655092592589</v>
       </c>
       <c r="P46" s="79"/>
@@ -9395,7 +9410,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M47,1,1), $F:$F, "&lt;="&amp;DATE(M47,12,31))</f>
+        <f t="shared" si="0"/>
         <v>96.097395833333323</v>
       </c>
       <c r="P47" s="77"/>
@@ -9443,7 +9458,7 @@
         <v>50</v>
       </c>
       <c r="O48" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M48,1,1), $F:$F, "&lt;="&amp;DATE(M48,12,31))</f>
+        <f t="shared" si="0"/>
         <v>76.722939814814836</v>
       </c>
       <c r="P48" s="79"/>
@@ -9491,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="O49" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M49,1,1), $F:$F, "&lt;="&amp;DATE(M49,12,31))</f>
+        <f t="shared" si="0"/>
         <v>29.277777777777782</v>
       </c>
       <c r="P49" s="77"/>
@@ -9539,7 +9554,7 @@
         <v>42</v>
       </c>
       <c r="O50" s="78">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M50,1,1), $F:$F, "&lt;="&amp;DATE(M50,12,31))</f>
+        <f t="shared" si="0"/>
         <v>33.481250000000003</v>
       </c>
       <c r="P50" s="79"/>
@@ -9587,7 +9602,7 @@
         <v>16</v>
       </c>
       <c r="O51" s="76">
-        <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M51,1,1), $F:$F, "&lt;="&amp;DATE(M51,12,31))</f>
+        <f t="shared" si="0"/>
         <v>40.547222222222231</v>
       </c>
       <c r="P51" s="77"/>
@@ -21768,22 +21783,22 @@
     <mergeCell ref="O51:P51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 C3:L1048576 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>OR(ISNUMBER(FIND("NES",C1)),    ISNUMBER(FIND("SNES",C1)),    ISNUMBER(FIND("N64",C1)),    ISNUMBER(FIND("GC",C1)),    ISNUMBER(FIND("Wii",C1)),    ISNUMBER(FIND("Wii U",C1)),    ISNUMBER(FIND("Switch",C1)),    ISNUMBER(FIND("Switch 2",C1)),    ISNUMBER(FIND("GB",C1)),    ISNUMBER(FIND("GBC",C1)),    ISNUMBER(FIND("GBA",C1)),    ISNUMBER(FIND("DS",C1)),    ISNUMBER(FIND("3DS",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 S26:T29 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 S26:T29">
     <cfRule type="expression" dxfId="23" priority="18">
       <formula>OR(ISNUMBER(FIND("X One",C1)),    ISNUMBER(FIND("X Series",C1)),    ISNUMBER(FIND("X 360",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="22" priority="17">
       <formula>OR(ISNUMBER(FIND("PS1",C1)),    ISNUMBER(FIND("PS2",C1)),    ISNUMBER(FIND("PS3",C1)),    ISNUMBER(FIND("PS4",C1)),    ISNUMBER(FIND("PSP",C1)),    ISNUMBER(FIND("Vita",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 S26:T29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 C3:L1048576 M24:N34 O26:Q29 S26:T29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576">
     <cfRule type="expression" dxfId="21" priority="19">
       <formula>ISNUMBER(FIND("PC",C1))</formula>
     </cfRule>
@@ -21791,7 +21806,7 @@
       <formula>ISNUMBER(FIND("MD",C1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M14 H1:H1048576">
+  <conditionalFormatting sqref="H1:H1048576 M4:M14">
     <cfRule type="expression" dxfId="19" priority="11">
       <formula>OR(ISNUMBER(FIND("11",H1)),)</formula>
     </cfRule>
@@ -21813,7 +21828,7 @@
       <formula>NOT(ISERROR(SEARCH("Não",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M22 M24:M34 M37:M53 M58:M1048576 I1:I1048576">
+  <conditionalFormatting sqref="M1:M22 I1:I1048576 M24:M34 M37:M53 M58:M1048576">
     <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="Fácil">
       <formula>NOT(ISERROR(SEARCH("Fácil",I1)))</formula>
     </cfRule>
@@ -22488,7 +22503,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>383</v>
+        <v>513</v>
       </c>
       <c r="F18" s="22">
         <v>15</v>
@@ -22526,7 +22541,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="F19" s="22">
         <v>16</v>
@@ -22564,7 +22579,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>509</v>
+        <v>405</v>
       </c>
       <c r="F20" s="22">
         <v>17</v>
@@ -22602,7 +22617,7 @@
         <v>7</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F21" s="22">
         <v>18</v>
@@ -22640,7 +22655,7 @@
         <v>7</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>406</v>
+        <v>510</v>
       </c>
       <c r="F22" s="22">
         <v>19</v>
@@ -22675,10 +22690,10 @@
         <v>20</v>
       </c>
       <c r="C23" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="F23" s="22">
         <v>20</v>
@@ -22716,7 +22731,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="J24" s="22">
         <v>21</v>
@@ -22745,7 +22760,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="J25" s="22">
         <v>22</v>
@@ -22774,7 +22789,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J26" s="22">
         <v>23</v>
@@ -22803,7 +22818,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>508</v>
+        <v>386</v>
       </c>
       <c r="J27" s="22">
         <v>24</v>
@@ -22832,7 +22847,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>380</v>
+        <v>508</v>
       </c>
       <c r="N28" s="22">
         <v>25</v>
@@ -22845,6 +22860,15 @@
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="22">
+        <v>26</v>
+      </c>
+      <c r="C29" s="21">
+        <v>6</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>380</v>
+      </c>
       <c r="N29" s="22">
         <v>26</v>
       </c>

--- a/jogos/Lista de Jogos Finalizados.xlsx
+++ b/jogos/Lista de Jogos Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855241B6-70CF-4C8F-B759-6B616FCDB7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5B0087-1B15-4F29-919B-B003F8C9B0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{185F8663-3FF1-4EF9-AA90-43B25B82DF02}"/>
   </bookViews>
@@ -2956,7 +2956,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="514">
   <si>
     <t>Nº</t>
   </si>
@@ -3676,9 +3676,6 @@
   </si>
   <si>
     <t>The Legend of Zelda: Oracle of Seasons</t>
-  </si>
-  <si>
-    <t>The Legend of Zelda: Tears of the Kigdom</t>
   </si>
   <si>
     <t>Harry Potter and the Sorcerer's Stone</t>
@@ -6771,7 +6768,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I1" s="34" t="s">
         <v>5</v>
@@ -6916,13 +6913,13 @@
         <v>385</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>120</v>
@@ -6960,7 +6957,7 @@
         <v>86</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T4" s="15">
         <f>COUNTIF(D:D,"Switch")</f>
@@ -6979,13 +6976,13 @@
         <v>384</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>65</v>
@@ -7016,7 +7013,7 @@
         <v>58</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q5" s="15">
         <f>COUNTIF(C:C,"3DS")</f>
@@ -7043,7 +7040,7 @@
         <v>383</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>156</v>
@@ -7080,14 +7077,14 @@
         <v>64</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q6" s="15">
         <f>COUNTIF(C:C,"Switch")</f>
         <v>41</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T6" s="15">
         <f>COUNTIF(D:D,"PS4")</f>
@@ -7107,13 +7104,13 @@
         <v>382</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>30</v>
@@ -7144,14 +7141,14 @@
         <v>90</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q7" s="15">
         <f>COUNTIF(C:C,"PS4")</f>
         <v>36</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T7" s="15">
         <f>COUNTIF(D:D,"3DS")</f>
@@ -7171,13 +7168,13 @@
         <v>381</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>28</v>
@@ -7209,14 +7206,14 @@
         <v>91</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q8" s="15">
         <f>COUNTIF(C:C,"Switch 2")</f>
         <v>33</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T8" s="15">
         <f>COUNTIF(D:D,"PS3")</f>
@@ -7236,13 +7233,13 @@
         <v>380</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>87</v>
@@ -7273,14 +7270,14 @@
         <v>37</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q9" s="15">
         <f>COUNTIF(C:C,"PS3")</f>
         <v>31</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T9" s="15">
         <f>COUNTIF(D:D,"DS")</f>
@@ -7300,13 +7297,13 @@
         <v>379</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -7337,14 +7334,14 @@
         <v>18</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q10" s="15">
         <f>COUNTIF(C:C,"DS")</f>
         <v>21</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T10" s="15">
         <f>COUNTIF(D:D,"GBA")</f>
@@ -7364,13 +7361,13 @@
         <v>378</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>29</v>
@@ -7388,7 +7385,7 @@
         <v>33</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>38</v>
@@ -7401,14 +7398,14 @@
         <v>7</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q11" s="15">
         <f>COUNTIF(C:C,"Wii")</f>
         <v>11</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T11" s="15">
         <f>COUNTIF(D:D,"N64")</f>
@@ -7428,13 +7425,13 @@
         <v>377</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -7465,14 +7462,14 @@
         <v>2</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q12" s="15">
         <f>COUNTIF(C:C,"SNES")</f>
         <v>11</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T12" s="15">
         <f>COUNTIF(D:D,"SNES")</f>
@@ -7492,13 +7489,13 @@
         <v>376</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -7529,14 +7526,14 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q13" s="15">
         <f>COUNTIF(C:C,"Vita")</f>
         <v>10</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="T13" s="15">
         <f>COUNTIF(D:D,"PS1")</f>
@@ -7556,13 +7553,13 @@
         <v>375</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>23</v>
@@ -7593,14 +7590,14 @@
         <v>1</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q14" s="15">
         <f>COUNTIF(C:C,"X 360")</f>
         <v>8</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="T14" s="15">
         <f>COUNTIF(D:D,"Vita")</f>
@@ -7620,13 +7617,13 @@
         <v>374</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>23</v>
@@ -7657,14 +7654,14 @@
         <v>385</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q15" s="15">
         <f>COUNTIF(C:C,"N64")</f>
         <v>7</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T15" s="15">
         <f>COUNTIF(D:D,"GB")</f>
@@ -7684,13 +7681,13 @@
         <v>373</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>21</v>
@@ -7708,7 +7705,7 @@
         <v>32</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>37</v>
@@ -7716,14 +7713,14 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="P16" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q16" s="15">
         <f>COUNTIF(C:C,"Wii U")</f>
         <v>7</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T16" s="15">
         <f>COUNTIF(D:D,"X 360")</f>
@@ -7743,13 +7740,13 @@
         <v>372</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>21</v>
@@ -7779,14 +7776,14 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q17" s="15">
         <f>COUNTIF(C:C,"GBA")</f>
         <v>6</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T17" s="15">
         <f>COUNTIF(D:D,"Wii U")</f>
@@ -7806,13 +7803,13 @@
         <v>371</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>21</v>
@@ -7843,14 +7840,14 @@
         <v>4</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q18" s="15">
         <f>COUNTIF(C:C,"X Series")</f>
         <v>6</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T18" s="15">
         <f>COUNTIF(D:D,"Switch 2")</f>
@@ -7870,13 +7867,13 @@
         <v>370</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>21</v>
@@ -7907,14 +7904,14 @@
         <v>39</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q19" s="15">
         <f>COUNTIF(C:C,"GB")</f>
         <v>5</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="T19" s="15">
         <f>COUNTIF(D:D,"Wii")</f>
@@ -7934,13 +7931,13 @@
         <v>369</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>21</v>
@@ -7972,14 +7969,14 @@
         <v>253</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q20" s="15">
         <f>COUNTIF(C:C,"PS1")</f>
         <v>5</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="T20" s="15">
         <f>COUNTIF(D:D,"X Series")</f>
@@ -7999,13 +7996,13 @@
         <v>368</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>21</v>
@@ -8043,7 +8040,7 @@
         <v>5</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T21" s="15">
         <f>COUNTIF(D:D,"GBC")</f>
@@ -8063,13 +8060,13 @@
         <v>367</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>22</v>
@@ -8101,14 +8098,14 @@
         <v>385</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q22" s="15">
         <f>COUNTIF(C:C,"GC")</f>
         <v>4</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T22" s="15">
         <f>COUNTIF(D:D,"PS2")</f>
@@ -8128,13 +8125,13 @@
         <v>366</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>22</v>
@@ -8158,7 +8155,7 @@
         <v>38</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q23" s="15">
         <f>COUNTIF(C:C,"GBC")</f>
@@ -8178,7 +8175,7 @@
         <v>365</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>20</v>
@@ -8209,20 +8206,20 @@
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N24" s="44" t="s">
         <v>51</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q24" s="15">
         <f>COUNTIF(C:C,"X One")</f>
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="T24" s="15">
         <f>COUNTIF(D:D,"GC")</f>
@@ -8235,13 +8232,13 @@
         <v>364</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>27</v>
@@ -8266,21 +8263,21 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="49" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N25" s="42">
         <f>COUNTIFS(B:B,"*[P]*")</f>
         <v>20</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q25" s="15">
         <f>COUNTIF(C:C,"PS2")</f>
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T25" s="15">
         <f>COUNTIF(D:D,"MD")</f>
@@ -8293,7 +8290,7 @@
         <v>363</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>20</v>
@@ -8324,7 +8321,7 @@
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="48" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N26" s="42">
         <f>COUNTIFS(B:B,"*[D]*")</f>
@@ -8351,13 +8348,13 @@
         <v>362</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>27</v>
@@ -8382,21 +8379,21 @@
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N27" s="42">
         <f>N29-N28</f>
         <v>333</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q27" s="15">
         <f>COUNTIF(C:C,"MD")</f>
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="T27" s="15">
         <f>COUNTIF(D:D,"X One")</f>
@@ -8409,13 +8406,13 @@
         <v>361</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>23</v>
@@ -8440,7 +8437,7 @@
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N28" s="42">
         <f>COUNTIFS(B:B,"*(*")</f>
@@ -8467,7 +8464,7 @@
         <v>360</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>20</v>
@@ -8491,13 +8488,13 @@
         <v>32</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>37</v>
       </c>
       <c r="M29" s="43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N29" s="47">
         <f>COUNT(A:A)</f>
@@ -8510,10 +8507,10 @@
         <v>359</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>227</v>
@@ -8561,13 +8558,13 @@
         <v>358</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>23</v>
@@ -8598,14 +8595,14 @@
         <v>0</v>
       </c>
       <c r="P31" s="33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q31" s="15" cm="1">
         <f t="array" ref="Q31">SUM(SUMIF($P$4:$P$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$Q$4:$Q$27))</f>
         <v>197</v>
       </c>
       <c r="S31" s="33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="T31" s="15" cm="1">
         <f t="array" ref="T31">SUM(SUMIF($S$4:$S$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$T$4:$T$27))</f>
@@ -8618,13 +8615,13 @@
         <v>357</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>23</v>
@@ -8649,21 +8646,21 @@
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="52" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N32" s="42">
         <f>COUNTIF(K:K,"Sim")</f>
         <v>290</v>
       </c>
       <c r="P32" s="58" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q32" s="15" cm="1">
         <f t="array" ref="Q32">SUM(SUMIF($P$4:$P$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$Q$4:$Q$27))</f>
         <v>87</v>
       </c>
       <c r="S32" s="58" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="T32" s="15" cm="1">
         <f t="array" ref="T32">SUM(SUMIF($S$4:$S$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$T$4:$T$27))</f>
@@ -8676,13 +8673,13 @@
         <v>356</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>24</v>
@@ -8707,21 +8704,21 @@
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N33" s="42">
         <f>COUNTIF(K:K,"Não")</f>
         <v>95</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q33" s="15" cm="1">
         <f t="array" ref="Q33">SUM(SUMIF($P$4:$P$27,{"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>15</v>
       </c>
       <c r="S33" s="59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="T33" s="15" cm="1">
         <f t="array" ref="T33">SUM(SUMIF($S$4:$S$27,{"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8734,13 +8731,13 @@
         <v>355</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>23</v>
@@ -8792,13 +8789,13 @@
         <v>354</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>27</v>
@@ -8825,14 +8822,14 @@
       <c r="M35"/>
       <c r="N35"/>
       <c r="P35" s="62" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q35" s="15" cm="1">
         <f t="array" ref="Q35">SUM($Q$4:$Q$27)-SUM(SUMIF($P$4:$P$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>0</v>
       </c>
       <c r="S35" s="62" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T35" s="15" cm="1">
         <f t="array" ref="T35">SUM($T$4:$T$27)-SUM(SUMIF($S$4:$S$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8845,13 +8842,13 @@
         <v>353</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>24</v>
@@ -8898,13 +8895,13 @@
         <v>352</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>29</v>
@@ -8938,13 +8935,13 @@
         <v>351</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>23</v>
@@ -8972,10 +8969,10 @@
         <v>53</v>
       </c>
       <c r="N38" s="55" t="s">
+        <v>490</v>
+      </c>
+      <c r="O38" s="82" t="s">
         <v>491</v>
-      </c>
-      <c r="O38" s="82" t="s">
-        <v>492</v>
       </c>
       <c r="P38" s="83"/>
     </row>
@@ -8985,13 +8982,13 @@
         <v>350</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>65</v>
@@ -9034,13 +9031,13 @@
         <v>349</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>22</v>
@@ -9083,13 +9080,13 @@
         <v>348</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>23</v>
@@ -9132,13 +9129,13 @@
         <v>347</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>21</v>
@@ -9181,13 +9178,13 @@
         <v>346</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>23</v>
@@ -9229,13 +9226,13 @@
         <v>345</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>23</v>
@@ -9277,13 +9274,13 @@
         <v>344</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>28</v>
@@ -9325,13 +9322,13 @@
         <v>343</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>107</v>
@@ -9349,7 +9346,7 @@
         <v>33</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>37</v>
@@ -9376,10 +9373,10 @@
         <v>99</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>21</v>
@@ -9421,13 +9418,13 @@
         <v>341</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>21</v>
@@ -9469,13 +9466,13 @@
         <v>340</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>23</v>
@@ -9517,7 +9514,7 @@
         <v>339</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>20</v>
@@ -9565,7 +9562,7 @@
         <v>338</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>20</v>
@@ -9589,7 +9586,7 @@
         <v>32</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>37</v>
@@ -9613,13 +9610,13 @@
         <v>337</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>30</v>
@@ -9661,7 +9658,7 @@
         <v>336</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>20</v>
@@ -9697,13 +9694,13 @@
         <v>335</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>69</v>
@@ -9721,7 +9718,7 @@
         <v>32</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>38</v>
@@ -9733,13 +9730,13 @@
         <v>334</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>69</v>
@@ -9757,7 +9754,7 @@
         <v>32</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>38</v>
@@ -9769,13 +9766,13 @@
         <v>333</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>69</v>
@@ -9793,7 +9790,7 @@
         <v>32</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>38</v>
@@ -9805,13 +9802,13 @@
         <v>332</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>69</v>
@@ -9829,7 +9826,7 @@
         <v>32</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>38</v>
@@ -9841,13 +9838,13 @@
         <v>331</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>69</v>
@@ -9865,7 +9862,7 @@
         <v>32</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>38</v>
@@ -9877,13 +9874,13 @@
         <v>330</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>69</v>
@@ -9901,7 +9898,7 @@
         <v>32</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>38</v>
@@ -9919,7 +9916,7 @@
         <v>20</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>22</v>
@@ -9949,13 +9946,13 @@
         <v>328</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>69</v>
@@ -9973,7 +9970,7 @@
         <v>32</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>38</v>
@@ -9985,13 +9982,13 @@
         <v>327</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>69</v>
@@ -10009,7 +10006,7 @@
         <v>32</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>37</v>
@@ -10027,7 +10024,7 @@
         <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>21</v>
@@ -10057,7 +10054,7 @@
         <v>325</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>20</v>
@@ -10093,7 +10090,7 @@
         <v>324</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>20</v>
@@ -10129,7 +10126,7 @@
         <v>323</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>20</v>
@@ -10165,7 +10162,7 @@
         <v>322</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>20</v>
@@ -10201,7 +10198,7 @@
         <v>321</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>20</v>
@@ -10225,7 +10222,7 @@
         <v>32</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>37</v>
@@ -10237,7 +10234,7 @@
         <v>320</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>20</v>
@@ -10273,7 +10270,7 @@
         <v>319</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
@@ -10309,7 +10306,7 @@
         <v>318</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>20</v>
@@ -10333,7 +10330,7 @@
         <v>33</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>37</v>
@@ -10345,13 +10342,13 @@
         <v>317</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>22</v>
@@ -10381,13 +10378,13 @@
         <v>316</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>27</v>
@@ -10417,7 +10414,7 @@
         <v>315</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>20</v>
@@ -10441,7 +10438,7 @@
         <v>33</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>37</v>
@@ -10453,13 +10450,13 @@
         <v>314</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>69</v>
@@ -10477,7 +10474,7 @@
         <v>33</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>38</v>
@@ -10489,13 +10486,13 @@
         <v>313</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>185</v>
@@ -10513,7 +10510,7 @@
         <v>34</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>38</v>
@@ -10525,13 +10522,13 @@
         <v>312</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>21</v>
@@ -10561,7 +10558,7 @@
         <v>311</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>20</v>
@@ -10597,13 +10594,13 @@
         <v>310</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>21</v>
@@ -10633,13 +10630,13 @@
         <v>309</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>23</v>
@@ -10669,13 +10666,13 @@
         <v>308</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>21</v>
@@ -10705,13 +10702,13 @@
         <v>307</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>21</v>
@@ -10741,13 +10738,13 @@
         <v>306</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>23</v>
@@ -10777,13 +10774,13 @@
         <v>305</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>23</v>
@@ -10813,13 +10810,13 @@
         <v>304</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>157</v>
@@ -10849,13 +10846,13 @@
         <v>303</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>21</v>
@@ -10885,13 +10882,13 @@
         <v>302</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -10921,13 +10918,13 @@
         <v>301</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>23</v>
@@ -10957,13 +10954,13 @@
         <v>300</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>23</v>
@@ -10993,13 +10990,13 @@
         <v>299</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>69</v>
@@ -11017,7 +11014,7 @@
         <v>33</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>38</v>
@@ -11029,13 +11026,13 @@
         <v>298</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>23</v>
@@ -11065,13 +11062,13 @@
         <v>297</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>22</v>
@@ -11107,7 +11104,7 @@
         <v>20</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>107</v>
@@ -11143,7 +11140,7 @@
         <v>20</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>107</v>
@@ -11176,10 +11173,10 @@
         <v>230</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>22</v>
@@ -11251,7 +11248,7 @@
         <v>20</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>22</v>
@@ -11281,13 +11278,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>21</v>
@@ -11317,13 +11314,13 @@
         <v>290</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>27</v>
@@ -11359,7 +11356,7 @@
         <v>20</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>30</v>
@@ -11389,13 +11386,13 @@
         <v>288</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>30</v>
@@ -11425,7 +11422,7 @@
         <v>287</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>20</v>
@@ -11533,13 +11530,13 @@
         <v>284</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>23</v>
@@ -11569,13 +11566,13 @@
         <v>283</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>23</v>
@@ -11608,10 +11605,10 @@
         <v>218</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>23</v>
@@ -11644,10 +11641,10 @@
         <v>219</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -11677,13 +11674,13 @@
         <v>280</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>23</v>
@@ -11713,7 +11710,7 @@
         <v>279</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>20</v>
@@ -11749,7 +11746,7 @@
         <v>278</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>20</v>
@@ -11821,7 +11818,7 @@
         <v>276</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>20</v>
@@ -11857,13 +11854,13 @@
         <v>275</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>24</v>
@@ -12001,13 +11998,13 @@
         <v>271</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>23</v>
@@ -12217,7 +12214,7 @@
         <v>265</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>20</v>
@@ -12361,7 +12358,7 @@
         <v>261</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>20</v>
@@ -12397,7 +12394,7 @@
         <v>260</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>20</v>
@@ -12469,7 +12466,7 @@
         <v>258</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>20</v>
@@ -12685,7 +12682,7 @@
         <v>252</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>20</v>
@@ -12832,10 +12829,10 @@
         <v>191</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>23</v>
@@ -12865,13 +12862,13 @@
         <v>247</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>23</v>
@@ -12901,13 +12898,13 @@
         <v>246</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>157</v>
@@ -12937,13 +12934,13 @@
         <v>245</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>24</v>
@@ -12976,10 +12973,10 @@
         <v>189</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>24</v>
@@ -13009,13 +13006,13 @@
         <v>243</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>87</v>
@@ -13048,10 +13045,10 @@
         <v>188</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>29</v>
@@ -13081,13 +13078,13 @@
         <v>241</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>23</v>
@@ -13117,13 +13114,13 @@
         <v>240</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>120</v>
@@ -13153,13 +13150,13 @@
         <v>239</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>27</v>
@@ -13192,10 +13189,10 @@
         <v>187</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>22</v>
@@ -13261,7 +13258,7 @@
         <v>236</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>20</v>
@@ -13300,10 +13297,10 @@
         <v>184</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>185</v>
@@ -13336,10 +13333,10 @@
         <v>183</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>21</v>
@@ -13369,13 +13366,13 @@
         <v>233</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>23</v>
@@ -13408,10 +13405,10 @@
         <v>182</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>27</v>
@@ -13444,10 +13441,10 @@
         <v>181</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>30</v>
@@ -13477,13 +13474,13 @@
         <v>230</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>87</v>
@@ -13516,10 +13513,10 @@
         <v>180</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>23</v>
@@ -13552,10 +13549,10 @@
         <v>179</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>107</v>
@@ -13585,13 +13582,13 @@
         <v>227</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>177</v>
@@ -13621,13 +13618,13 @@
         <v>226</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>30</v>
@@ -13657,13 +13654,13 @@
         <v>225</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>27</v>
@@ -13693,13 +13690,13 @@
         <v>224</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>23</v>
@@ -13732,10 +13729,10 @@
         <v>176</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>23</v>
@@ -13765,13 +13762,13 @@
         <v>222</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>177</v>
@@ -13801,13 +13798,13 @@
         <v>221</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>107</v>
@@ -13840,10 +13837,10 @@
         <v>175</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>65</v>
@@ -13876,10 +13873,10 @@
         <v>174</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>23</v>
@@ -13912,10 +13909,10 @@
         <v>173</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>23</v>
@@ -13948,10 +13945,10 @@
         <v>172</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>65</v>
@@ -13984,10 +13981,10 @@
         <v>171</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>23</v>
@@ -14017,13 +14014,13 @@
         <v>215</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>21</v>
@@ -14053,13 +14050,13 @@
         <v>214</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>24</v>
@@ -14092,10 +14089,10 @@
         <v>169</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>21</v>
@@ -14128,10 +14125,10 @@
         <v>168</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>157</v>
@@ -14161,13 +14158,13 @@
         <v>211</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>22</v>
@@ -14200,10 +14197,10 @@
         <v>166</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>30</v>
@@ -14236,10 +14233,10 @@
         <v>165</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>24</v>
@@ -14269,13 +14266,13 @@
         <v>208</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>22</v>
@@ -14308,10 +14305,10 @@
         <v>164</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>25</v>
@@ -14344,10 +14341,10 @@
         <v>163</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>87</v>
@@ -14380,10 +14377,10 @@
         <v>162</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>21</v>
@@ -14416,10 +14413,10 @@
         <v>161</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>24</v>
@@ -14452,10 +14449,10 @@
         <v>160</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>22</v>
@@ -14485,13 +14482,13 @@
         <v>202</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>65</v>
@@ -14524,10 +14521,10 @@
         <v>159</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>30</v>
@@ -14557,13 +14554,13 @@
         <v>200</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>65</v>
@@ -14593,13 +14590,13 @@
         <v>199</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>24</v>
@@ -14632,10 +14629,10 @@
         <v>155</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>23</v>
@@ -14668,10 +14665,10 @@
         <v>154</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>30</v>
@@ -14704,10 +14701,10 @@
         <v>216</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>30</v>
@@ -14737,13 +14734,13 @@
         <v>195</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>157</v>
@@ -14776,10 +14773,10 @@
         <v>153</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>24</v>
@@ -14812,10 +14809,10 @@
         <v>152</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>21</v>
@@ -14845,13 +14842,13 @@
         <v>192</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>21</v>
@@ -14881,13 +14878,13 @@
         <v>191</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>120</v>
@@ -14953,7 +14950,7 @@
         <v>189</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>156</v>
@@ -15064,10 +15061,10 @@
         <v>147</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>23</v>
@@ -15100,10 +15097,10 @@
         <v>146</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>87</v>
@@ -15136,10 +15133,10 @@
         <v>145</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>23</v>
@@ -15172,10 +15169,10 @@
         <v>144</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>87</v>
@@ -15208,10 +15205,10 @@
         <v>143</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>21</v>
@@ -15244,10 +15241,10 @@
         <v>150</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>23</v>
@@ -15277,13 +15274,13 @@
         <v>180</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>23</v>
@@ -15313,13 +15310,13 @@
         <v>179</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>21</v>
@@ -15352,10 +15349,10 @@
         <v>142</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>23</v>
@@ -15388,10 +15385,10 @@
         <v>141</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>23</v>
@@ -15424,10 +15421,10 @@
         <v>140</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>23</v>
@@ -15460,10 +15457,10 @@
         <v>139</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>23</v>
@@ -15496,10 +15493,10 @@
         <v>138</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>23</v>
@@ -15532,10 +15529,10 @@
         <v>137</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>23</v>
@@ -15565,13 +15562,13 @@
         <v>172</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>21</v>
@@ -15604,10 +15601,10 @@
         <v>136</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>23</v>
@@ -15637,13 +15634,13 @@
         <v>170</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>23</v>
@@ -15676,10 +15673,10 @@
         <v>135</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>23</v>
@@ -15709,13 +15706,13 @@
         <v>168</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>23</v>
@@ -15748,10 +15745,10 @@
         <v>134</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>23</v>
@@ -15784,10 +15781,10 @@
         <v>133</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>107</v>
@@ -15820,10 +15817,10 @@
         <v>132</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>23</v>
@@ -15853,13 +15850,13 @@
         <v>164</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>23</v>
@@ -15889,13 +15886,13 @@
         <v>163</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>23</v>
@@ -15925,13 +15922,13 @@
         <v>162</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>23</v>
@@ -15964,10 +15961,10 @@
         <v>131</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>23</v>
@@ -16000,10 +15997,10 @@
         <v>130</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>23</v>
@@ -16036,10 +16033,10 @@
         <v>129</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>23</v>
@@ -16072,10 +16069,10 @@
         <v>128</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>23</v>
@@ -16108,10 +16105,10 @@
         <v>127</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>23</v>
@@ -16141,13 +16138,13 @@
         <v>156</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>22</v>
@@ -16180,10 +16177,10 @@
         <v>126</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>21</v>
@@ -16216,10 +16213,10 @@
         <v>238</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>22</v>
@@ -16252,10 +16249,10 @@
         <v>239</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>22</v>
@@ -16288,10 +16285,10 @@
         <v>125</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>23</v>
@@ -16324,10 +16321,10 @@
         <v>124</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>23</v>
@@ -16360,10 +16357,10 @@
         <v>123</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>23</v>
@@ -16396,10 +16393,10 @@
         <v>122</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>22</v>
@@ -16429,13 +16426,13 @@
         <v>148</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>23</v>
@@ -16468,10 +16465,10 @@
         <v>121</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>23</v>
@@ -16504,10 +16501,10 @@
         <v>119</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>23</v>
@@ -16537,13 +16534,13 @@
         <v>145</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>27</v>
@@ -16576,10 +16573,10 @@
         <v>117</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>120</v>
@@ -16609,13 +16606,13 @@
         <v>143</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>21</v>
@@ -16648,10 +16645,10 @@
         <v>116</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>23</v>
@@ -16681,13 +16678,13 @@
         <v>141</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>23</v>
@@ -16720,10 +16717,10 @@
         <v>115</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>23</v>
@@ -16756,10 +16753,10 @@
         <v>114</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>28</v>
@@ -16792,10 +16789,10 @@
         <v>113</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>23</v>
@@ -16828,10 +16825,10 @@
         <v>112</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>23</v>
@@ -16864,10 +16861,10 @@
         <v>111</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>23</v>
@@ -16900,10 +16897,10 @@
         <v>110</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>22</v>
@@ -16936,10 +16933,10 @@
         <v>109</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>21</v>
@@ -16972,10 +16969,10 @@
         <v>106</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>21</v>
@@ -17008,10 +17005,10 @@
         <v>105</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>30</v>
@@ -17044,10 +17041,10 @@
         <v>104</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>30</v>
@@ -17080,10 +17077,10 @@
         <v>103</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>22</v>
@@ -17116,10 +17113,10 @@
         <v>102</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>107</v>
@@ -17152,10 +17149,10 @@
         <v>100</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>65</v>
@@ -17188,10 +17185,10 @@
         <v>99</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>27</v>
@@ -17221,7 +17218,7 @@
         <v>126</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>20</v>
@@ -17260,10 +17257,10 @@
         <v>98</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>23</v>
@@ -17293,13 +17290,13 @@
         <v>124</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>27</v>
@@ -17332,10 +17329,10 @@
         <v>96</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>27</v>
@@ -17368,7 +17365,7 @@
         <v>95</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>227</v>
@@ -17401,10 +17398,10 @@
         <v>121</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>227</v>
@@ -17440,10 +17437,10 @@
         <v>94</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>21</v>
@@ -17473,13 +17470,13 @@
         <v>119</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>27</v>
@@ -17512,10 +17509,10 @@
         <v>93</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>24</v>
@@ -17548,10 +17545,10 @@
         <v>92</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>23</v>
@@ -17584,10 +17581,10 @@
         <v>90</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>27</v>
@@ -17620,10 +17617,10 @@
         <v>89</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>23</v>
@@ -17656,10 +17653,10 @@
         <v>88</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>24</v>
@@ -17689,13 +17686,13 @@
         <v>113</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>22</v>
@@ -17728,10 +17725,10 @@
         <v>86</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>23</v>
@@ -17764,10 +17761,10 @@
         <v>85</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>23</v>
@@ -17800,10 +17797,10 @@
         <v>84</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>28</v>
@@ -17836,10 +17833,10 @@
         <v>83</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>23</v>
@@ -17872,10 +17869,10 @@
         <v>82</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>87</v>
@@ -17908,10 +17905,10 @@
         <v>81</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>23</v>
@@ -17944,10 +17941,10 @@
         <v>80</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>23</v>
@@ -17980,10 +17977,10 @@
         <v>79</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>28</v>
@@ -18016,10 +18013,10 @@
         <v>78</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>23</v>
@@ -18052,10 +18049,10 @@
         <v>77</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>21</v>
@@ -18085,13 +18082,13 @@
         <v>102</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>65</v>
@@ -18124,10 +18121,10 @@
         <v>75</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>24</v>
@@ -18160,10 +18157,10 @@
         <v>76</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>24</v>
@@ -18196,7 +18193,7 @@
         <v>74</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>227</v>
@@ -18232,10 +18229,10 @@
         <v>73</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>23</v>
@@ -18268,10 +18265,10 @@
         <v>72</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>23</v>
@@ -18304,10 +18301,10 @@
         <v>68</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>23</v>
@@ -18340,10 +18337,10 @@
         <v>67</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>30</v>
@@ -18376,10 +18373,10 @@
         <v>235</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>22</v>
@@ -18412,10 +18409,10 @@
         <v>236</v>
       </c>
       <c r="C296" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>22</v>
@@ -18445,13 +18442,13 @@
         <v>92</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>69</v>
@@ -18484,10 +18481,10 @@
         <v>234</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>22</v>
@@ -18520,10 +18517,10 @@
         <v>64</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>23</v>
@@ -18556,10 +18553,10 @@
         <v>63</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>65</v>
@@ -18592,10 +18589,10 @@
         <v>62</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>22</v>
@@ -18628,10 +18625,10 @@
         <v>61</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>21</v>
@@ -18664,10 +18661,10 @@
         <v>60</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>21</v>
@@ -18700,10 +18697,10 @@
         <v>58</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>21</v>
@@ -18736,10 +18733,10 @@
         <v>91</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>27</v>
@@ -18772,10 +18769,10 @@
         <v>57</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>23</v>
@@ -18808,10 +18805,10 @@
         <v>56</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>21</v>
@@ -18841,13 +18838,13 @@
         <v>81</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>21</v>
@@ -18880,10 +18877,10 @@
         <v>55</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>28</v>
@@ -18916,10 +18913,10 @@
         <v>54</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>27</v>
@@ -18988,10 +18985,10 @@
         <v>18</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>23</v>
@@ -19024,10 +19021,10 @@
         <v>237</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>22</v>
@@ -19057,13 +19054,13 @@
         <v>75</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>21</v>
@@ -19093,7 +19090,7 @@
         <v>74</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>20</v>
@@ -19129,13 +19126,13 @@
         <v>73</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>23</v>
@@ -19168,10 +19165,10 @@
         <v>17</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>29</v>
@@ -19204,10 +19201,10 @@
         <v>16</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>28</v>
@@ -19240,10 +19237,10 @@
         <v>15</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>27</v>
@@ -19276,10 +19273,10 @@
         <v>14</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>23</v>
@@ -19312,10 +19309,10 @@
         <v>13</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>23</v>
@@ -19417,7 +19414,7 @@
         <v>65</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>20</v>
@@ -19489,7 +19486,7 @@
         <v>63</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>20</v>
@@ -19525,7 +19522,7 @@
         <v>62</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>20</v>
@@ -19564,10 +19561,10 @@
         <v>8</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>23</v>
@@ -19600,10 +19597,10 @@
         <v>7</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>23</v>
@@ -19636,10 +19633,10 @@
         <v>6</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>24</v>
@@ -19669,13 +19666,13 @@
         <v>58</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>27</v>
@@ -19705,13 +19702,13 @@
         <v>57</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>65</v>
@@ -19741,13 +19738,13 @@
         <v>56</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>29</v>
@@ -19765,7 +19762,7 @@
         <v>52</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K333" s="1" t="s">
         <v>37</v>
@@ -19777,13 +19774,13 @@
         <v>55</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>29</v>
@@ -19801,7 +19798,7 @@
         <v>32</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K334" s="1" t="s">
         <v>37</v>
@@ -19813,13 +19810,13 @@
         <v>54</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>23</v>
@@ -19849,13 +19846,13 @@
         <v>53</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>65</v>
@@ -19873,7 +19870,7 @@
         <v>34</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K336" s="1" t="s">
         <v>37</v>
@@ -19885,13 +19882,13 @@
         <v>52</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>21</v>
@@ -19921,13 +19918,13 @@
         <v>51</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>157</v>
@@ -19945,7 +19942,7 @@
         <v>34</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K338" s="1" t="s">
         <v>37</v>
@@ -19957,13 +19954,13 @@
         <v>50</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>27</v>
@@ -19993,13 +19990,13 @@
         <v>49</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>27</v>
@@ -20029,13 +20026,13 @@
         <v>48</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>27</v>
@@ -20065,13 +20062,13 @@
         <v>47</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>27</v>
@@ -20101,13 +20098,13 @@
         <v>46</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>27</v>
@@ -20137,13 +20134,13 @@
         <v>45</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>27</v>
@@ -20173,13 +20170,13 @@
         <v>44</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>21</v>
@@ -20209,13 +20206,13 @@
         <v>43</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>27</v>
@@ -20245,13 +20242,13 @@
         <v>42</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>27</v>
@@ -20281,13 +20278,13 @@
         <v>41</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>65</v>
@@ -20317,13 +20314,13 @@
         <v>40</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>22</v>
@@ -20353,13 +20350,13 @@
         <v>39</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>27</v>
@@ -20389,13 +20386,13 @@
         <v>38</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>28</v>
@@ -20425,13 +20422,13 @@
         <v>37</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>30</v>
@@ -20461,13 +20458,13 @@
         <v>36</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>27</v>
@@ -20497,13 +20494,13 @@
         <v>35</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>65</v>
@@ -20533,13 +20530,13 @@
         <v>34</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>22</v>
@@ -20569,13 +20566,13 @@
         <v>33</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>30</v>
@@ -20593,7 +20590,7 @@
         <v>32</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K356" s="1" t="s">
         <v>37</v>
@@ -20605,13 +20602,13 @@
         <v>32</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>22</v>
@@ -20641,13 +20638,13 @@
         <v>31</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>22</v>
@@ -20677,13 +20674,13 @@
         <v>30</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>22</v>
@@ -20713,13 +20710,13 @@
         <v>29</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>22</v>
@@ -20749,13 +20746,13 @@
         <v>28</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>28</v>
@@ -20788,10 +20785,10 @@
         <v>122</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>22</v>
@@ -20821,13 +20818,13 @@
         <v>26</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>21</v>
@@ -20857,13 +20854,13 @@
         <v>25</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>30</v>
@@ -20881,7 +20878,7 @@
         <v>32</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K364" s="1" t="s">
         <v>37</v>
@@ -20893,13 +20890,13 @@
         <v>24</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>27</v>
@@ -20929,13 +20926,13 @@
         <v>23</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>27</v>
@@ -20965,13 +20962,13 @@
         <v>22</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>27</v>
@@ -21001,13 +20998,13 @@
         <v>21</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>27</v>
@@ -21037,13 +21034,13 @@
         <v>20</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>65</v>
@@ -21073,13 +21070,13 @@
         <v>19</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>27</v>
@@ -21109,13 +21106,13 @@
         <v>18</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>30</v>
@@ -21145,13 +21142,13 @@
         <v>17</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>22</v>
@@ -21181,13 +21178,13 @@
         <v>16</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>120</v>
@@ -21217,13 +21214,13 @@
         <v>15</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>23</v>
@@ -21253,13 +21250,13 @@
         <v>14</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>22</v>
@@ -21289,13 +21286,13 @@
         <v>13</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>30</v>
@@ -21328,10 +21325,10 @@
         <v>167</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>22</v>
@@ -21361,13 +21358,13 @@
         <v>11</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>23</v>
@@ -21400,10 +21397,10 @@
         <v>26</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>22</v>
@@ -21433,13 +21430,13 @@
         <v>9</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>25</v>
@@ -21469,13 +21466,13 @@
         <v>8</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>22</v>
@@ -21508,10 +21505,10 @@
         <v>158</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>65</v>
@@ -21541,13 +21538,13 @@
         <v>6</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>22</v>
@@ -21577,13 +21574,13 @@
         <v>5</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>30</v>
@@ -21616,10 +21613,10 @@
         <v>9</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>25</v>
@@ -21652,10 +21649,10 @@
         <v>97</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>27</v>
@@ -21685,13 +21682,13 @@
         <v>2</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>29</v>
@@ -21709,7 +21706,7 @@
         <v>34</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K387" s="1" t="s">
         <v>37</v>
@@ -21721,13 +21718,13 @@
         <v>1</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>23</v>
@@ -21905,59 +21902,59 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="84" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
       <c r="F2" s="84" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G2" s="84"/>
       <c r="H2" s="84"/>
       <c r="J2" s="84" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K2" s="84"/>
       <c r="L2" s="84"/>
       <c r="N2" s="84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O2" s="84"/>
       <c r="P2" s="84"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>1</v>
@@ -21971,7 +21968,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F4" s="22">
         <v>1</v>
@@ -21989,7 +21986,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N4" s="22">
         <v>1</v>
@@ -21998,7 +21995,7 @@
         <v>11</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22018,7 +22015,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J5" s="22">
         <v>2</v>
@@ -22027,7 +22024,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N5" s="22">
         <v>2</v>
@@ -22036,7 +22033,7 @@
         <v>10</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22047,7 +22044,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F6" s="22">
         <v>3</v>
@@ -22056,7 +22053,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J6" s="22">
         <v>3</v>
@@ -22065,7 +22062,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N6" s="22">
         <v>3</v>
@@ -22085,7 +22082,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F7" s="22">
         <v>4</v>
@@ -22094,7 +22091,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J7" s="22">
         <v>4</v>
@@ -22103,7 +22100,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N7" s="22">
         <v>4</v>
@@ -22123,7 +22120,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F8" s="22">
         <v>5</v>
@@ -22132,7 +22129,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J8" s="22">
         <v>5</v>
@@ -22141,7 +22138,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N8" s="22">
         <v>5</v>
@@ -22150,7 +22147,7 @@
         <v>10</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22170,7 +22167,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J9" s="22">
         <v>6</v>
@@ -22179,7 +22176,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N9" s="22">
         <v>6</v>
@@ -22188,7 +22185,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22199,7 +22196,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F10" s="22">
         <v>7</v>
@@ -22208,7 +22205,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J10" s="22">
         <v>7</v>
@@ -22217,7 +22214,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N10" s="22">
         <v>7</v>
@@ -22237,7 +22234,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F11" s="22">
         <v>8</v>
@@ -22255,7 +22252,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N11" s="22">
         <v>8</v>
@@ -22275,7 +22272,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F12" s="22">
         <v>9</v>
@@ -22313,7 +22310,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F13" s="22">
         <v>10</v>
@@ -22322,7 +22319,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J13" s="22">
         <v>10</v>
@@ -22331,7 +22328,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N13" s="22">
         <v>10</v>
@@ -22351,7 +22348,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F14" s="22">
         <v>11</v>
@@ -22360,7 +22357,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J14" s="22">
         <v>11</v>
@@ -22378,7 +22375,7 @@
         <v>10</v>
       </c>
       <c r="P14" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22389,7 +22386,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F15" s="22">
         <v>12</v>
@@ -22398,7 +22395,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J15" s="22">
         <v>12</v>
@@ -22407,7 +22404,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N15" s="22">
         <v>12</v>
@@ -22427,7 +22424,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F16" s="22">
         <v>13</v>
@@ -22436,7 +22433,7 @@
         <v>8</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J16" s="22">
         <v>13</v>
@@ -22445,7 +22442,7 @@
         <v>7</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N16" s="22">
         <v>13</v>
@@ -22454,7 +22451,7 @@
         <v>9</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22465,7 +22462,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F17" s="22">
         <v>14</v>
@@ -22474,7 +22471,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J17" s="22">
         <v>14</v>
@@ -22483,7 +22480,7 @@
         <v>7</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N17" s="22">
         <v>14</v>
@@ -22492,7 +22489,7 @@
         <v>9</v>
       </c>
       <c r="P17" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22503,7 +22500,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F18" s="22">
         <v>15</v>
@@ -22512,7 +22509,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J18" s="22">
         <v>15</v>
@@ -22521,7 +22518,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N18" s="22">
         <v>15</v>
@@ -22541,7 +22538,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F19" s="22">
         <v>16</v>
@@ -22550,7 +22547,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J19" s="22">
         <v>16</v>
@@ -22559,7 +22556,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N19" s="22">
         <v>16</v>
@@ -22579,7 +22576,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F20" s="22">
         <v>17</v>
@@ -22588,7 +22585,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J20" s="22">
         <v>17</v>
@@ -22597,7 +22594,7 @@
         <v>6</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N20" s="22">
         <v>17</v>
@@ -22617,7 +22614,7 @@
         <v>7</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F21" s="22">
         <v>18</v>
@@ -22626,7 +22623,7 @@
         <v>6</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J21" s="22">
         <v>18</v>
@@ -22635,7 +22632,7 @@
         <v>6</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N21" s="22">
         <v>18</v>
@@ -22644,7 +22641,7 @@
         <v>9</v>
       </c>
       <c r="P21" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22655,7 +22652,7 @@
         <v>7</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F22" s="22">
         <v>19</v>
@@ -22664,7 +22661,7 @@
         <v>6</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J22" s="22">
         <v>19</v>
@@ -22673,7 +22670,7 @@
         <v>6</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N22" s="22">
         <v>19</v>
@@ -22682,7 +22679,7 @@
         <v>9</v>
       </c>
       <c r="P22" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22693,7 +22690,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F23" s="22">
         <v>20</v>
@@ -22702,7 +22699,7 @@
         <v>6</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J23" s="22">
         <v>20</v>
@@ -22711,7 +22708,7 @@
         <v>6</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N23" s="22">
         <v>20</v>
@@ -22720,7 +22717,7 @@
         <v>9</v>
       </c>
       <c r="P23" s="27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22731,7 +22728,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J24" s="22">
         <v>21</v>
@@ -22740,7 +22737,7 @@
         <v>6</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N24" s="22">
         <v>21</v>
@@ -22749,7 +22746,7 @@
         <v>8</v>
       </c>
       <c r="P24" s="24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22760,7 +22757,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J25" s="22">
         <v>22</v>
@@ -22769,7 +22766,7 @@
         <v>5</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N25" s="22">
         <v>22</v>
@@ -22778,7 +22775,7 @@
         <v>8</v>
       </c>
       <c r="P25" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22789,7 +22786,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J26" s="22">
         <v>23</v>
@@ -22798,7 +22795,7 @@
         <v>4</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N26" s="22">
         <v>23</v>
@@ -22818,7 +22815,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J27" s="22">
         <v>24</v>
@@ -22827,7 +22824,7 @@
         <v>4</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N27" s="22">
         <v>24</v>
@@ -22836,7 +22833,7 @@
         <v>8</v>
       </c>
       <c r="P27" s="24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22847,7 +22844,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N28" s="22">
         <v>25</v>
@@ -22856,7 +22853,7 @@
         <v>8</v>
       </c>
       <c r="P28" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22867,7 +22864,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N29" s="22">
         <v>26</v>
@@ -22876,7 +22873,7 @@
         <v>8</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22898,7 +22895,7 @@
         <v>7</v>
       </c>
       <c r="P31" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22909,7 +22906,7 @@
         <v>7</v>
       </c>
       <c r="P32" s="24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22920,7 +22917,7 @@
         <v>7</v>
       </c>
       <c r="P33" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22942,7 +22939,7 @@
         <v>6</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22953,7 +22950,7 @@
         <v>6</v>
       </c>
       <c r="P36" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/jogos/Lista de Jogos Finalizados.xlsx
+++ b/jogos/Lista de Jogos Finalizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luiz\Desktop\Pasta Geral\0 - Antunes\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F802DA73-0107-4B77-98D7-E3288662AD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC501AF-D30F-4528-AFF1-2DCB7EDC5154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{185F8663-3FF1-4EF9-AA90-43B25B82DF02}"/>
   </bookViews>
@@ -2812,7 +2812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B380" authorId="0" shapeId="0" xr:uid="{FFEA8B50-8BE5-4432-9E86-88781EC185DB}">
+    <comment ref="B379" authorId="0" shapeId="0" xr:uid="{BC58D2F4-1FB1-4009-AFF9-637BDA34BE2B}">
       <text>
         <r>
           <rPr>
@@ -2864,7 +2864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B386" authorId="0" shapeId="0" xr:uid="{87BF3E65-A40C-4F4F-8E63-C289B89F88C8}">
+    <comment ref="B384" authorId="0" shapeId="0" xr:uid="{87BF3E65-A40C-4F4F-8E63-C289B89F88C8}">
       <text>
         <r>
           <rPr>
@@ -2877,7 +2877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K386" authorId="0" shapeId="0" xr:uid="{C92ACBB1-538F-4DD0-A24C-606FE09A0B7F}">
+    <comment ref="K384" authorId="0" shapeId="0" xr:uid="{C92ACBB1-538F-4DD0-A24C-606FE09A0B7F}">
       <text>
         <r>
           <rPr>
@@ -2890,7 +2890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B387" authorId="0" shapeId="0" xr:uid="{FEC0AA46-CF40-4E8B-96EC-32FD92A6C187}">
+    <comment ref="B386" authorId="0" shapeId="0" xr:uid="{FEC0AA46-CF40-4E8B-96EC-32FD92A6C187}">
       <text>
         <r>
           <rPr>
@@ -2903,7 +2903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B388" authorId="0" shapeId="0" xr:uid="{DBBF01AB-3DEB-474F-BE2C-0004D65C7098}">
+    <comment ref="B387" authorId="0" shapeId="0" xr:uid="{DBBF01AB-3DEB-474F-BE2C-0004D65C7098}">
       <text>
         <r>
           <rPr>
@@ -2916,7 +2916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K388" authorId="0" shapeId="0" xr:uid="{4D21C75F-2110-43A7-B304-82B5FE0DDB0B}">
+    <comment ref="K387" authorId="0" shapeId="0" xr:uid="{4D21C75F-2110-43A7-B304-82B5FE0DDB0B}">
       <text>
         <r>
           <rPr>
@@ -2956,7 +2956,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="515">
   <si>
     <t>Nº</t>
   </si>
@@ -3469,9 +3469,6 @@
   </si>
   <si>
     <t>Finalizar todos jogos</t>
-  </si>
-  <si>
-    <t>Dragon Quest XI - Echoes of na Elusive Age</t>
   </si>
   <si>
     <t>Resident Evil 0</t>
@@ -5434,6 +5431,9 @@
   </si>
   <si>
     <t>Mario Tennis Aces</t>
+  </si>
+  <si>
+    <t>Dragon Quest XI - Echoes of an Elusive Age</t>
   </si>
 </sst>
 </file>
@@ -6759,7 +6759,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E1" s="34" t="s">
         <v>2</v>
@@ -6771,7 +6771,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I1" s="34" t="s">
         <v>5</v>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T3" s="38" t="s">
         <v>0</v>
@@ -6916,13 +6916,13 @@
         <v>386</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
@@ -6946,7 +6946,7 @@
         <v>38</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N4" s="63">
         <f>COUNTIF(H:H,11)</f>
@@ -6960,7 +6960,7 @@
         <v>86</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="T4" s="15">
         <f>COUNTIF(D:D,"Switch")</f>
@@ -6979,13 +6979,13 @@
         <v>385</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>120</v>
@@ -7016,7 +7016,7 @@
         <v>58</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q5" s="15">
         <f>COUNTIF(C:C,"3DS")</f>
@@ -7042,13 +7042,13 @@
         <v>384</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>65</v>
@@ -7079,14 +7079,14 @@
         <v>64</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q6" s="15">
         <f>COUNTIF(C:C,"Switch")</f>
         <v>41</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T6" s="15">
         <f>COUNTIF(D:D,"PS4")</f>
@@ -7106,7 +7106,7 @@
         <v>383</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>156</v>
@@ -7143,14 +7143,14 @@
         <v>90</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q7" s="15">
         <f>COUNTIF(C:C,"PS4")</f>
         <v>36</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T7" s="15">
         <f>COUNTIF(D:D,"3DS")</f>
@@ -7170,13 +7170,13 @@
         <v>382</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>30</v>
@@ -7208,14 +7208,14 @@
         <v>91</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q8" s="15">
         <f>COUNTIF(C:C,"Switch 2")</f>
         <v>34</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="T8" s="15">
         <f>COUNTIF(D:D,"PS3")</f>
@@ -7235,13 +7235,13 @@
         <v>381</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>28</v>
@@ -7272,14 +7272,14 @@
         <v>37</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q9" s="15">
         <f>COUNTIF(C:C,"PS3")</f>
         <v>31</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T9" s="15">
         <f>COUNTIF(D:D,"DS")</f>
@@ -7299,13 +7299,13 @@
         <v>380</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>87</v>
@@ -7336,14 +7336,14 @@
         <v>18</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q10" s="15">
         <f>COUNTIF(C:C,"DS")</f>
         <v>21</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T10" s="15">
         <f>COUNTIF(D:D,"GBA")</f>
@@ -7363,13 +7363,13 @@
         <v>379</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>23</v>
@@ -7400,14 +7400,14 @@
         <v>8</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q11" s="15">
         <f>COUNTIF(C:C,"Wii")</f>
         <v>11</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T11" s="15">
         <f>COUNTIF(D:D,"N64")</f>
@@ -7427,13 +7427,13 @@
         <v>378</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>29</v>
@@ -7451,7 +7451,7 @@
         <v>33</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>38</v>
@@ -7464,14 +7464,14 @@
         <v>2</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q12" s="15">
         <f>COUNTIF(C:C,"SNES")</f>
         <v>11</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="T12" s="15">
         <f>COUNTIF(D:D,"SNES")</f>
@@ -7491,13 +7491,13 @@
         <v>377</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -7528,14 +7528,14 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q13" s="15">
         <f>COUNTIF(C:C,"Vita")</f>
         <v>10</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T13" s="15">
         <f>COUNTIF(D:D,"PS1")</f>
@@ -7555,13 +7555,13 @@
         <v>376</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>23</v>
@@ -7592,14 +7592,14 @@
         <v>1</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q14" s="15">
         <f>COUNTIF(C:C,"X 360")</f>
         <v>8</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T14" s="15">
         <f>COUNTIF(D:D,"Vita")</f>
@@ -7619,13 +7619,13 @@
         <v>375</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>23</v>
@@ -7656,14 +7656,14 @@
         <v>386</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q15" s="15">
         <f>COUNTIF(C:C,"N64")</f>
         <v>7</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="T15" s="15">
         <f>COUNTIF(D:D,"GB")</f>
@@ -7683,13 +7683,13 @@
         <v>374</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>23</v>
@@ -7715,14 +7715,14 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="P16" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q16" s="15">
         <f>COUNTIF(C:C,"Wii U")</f>
         <v>7</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="T16" s="15">
         <f>COUNTIF(D:D,"X 360")</f>
@@ -7742,13 +7742,13 @@
         <v>373</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>21</v>
@@ -7766,7 +7766,7 @@
         <v>32</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>37</v>
@@ -7778,14 +7778,14 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q17" s="15">
         <f>COUNTIF(C:C,"GBA")</f>
         <v>6</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T17" s="15">
         <f>COUNTIF(D:D,"Wii U")</f>
@@ -7805,13 +7805,13 @@
         <v>372</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>21</v>
@@ -7842,14 +7842,14 @@
         <v>4</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q18" s="15">
         <f>COUNTIF(C:C,"X Series")</f>
         <v>6</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T18" s="15">
         <f>COUNTIF(D:D,"Switch 2")</f>
@@ -7869,13 +7869,13 @@
         <v>371</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>21</v>
@@ -7906,21 +7906,21 @@
         <v>40</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q19" s="15">
         <f>COUNTIF(C:C,"GB")</f>
         <v>5</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T19" s="15">
         <f>COUNTIF(D:D,"Wii")</f>
         <v>6</v>
       </c>
       <c r="V19" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W19" s="69">
         <f>COUNTIF(E:E,"Sandbox")</f>
@@ -7933,13 +7933,13 @@
         <v>370</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>21</v>
@@ -7971,21 +7971,21 @@
         <v>253</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q20" s="15">
         <f>COUNTIF(C:C,"PS1")</f>
         <v>5</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T20" s="15">
         <f>COUNTIF(D:D,"X Series")</f>
         <v>6</v>
       </c>
       <c r="V20" s="75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W20" s="42">
         <f>COUNTIF(E:E,"Roguelike")</f>
@@ -7998,13 +7998,13 @@
         <v>369</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>21</v>
@@ -8042,14 +8042,14 @@
         <v>5</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="T21" s="15">
         <f>COUNTIF(D:D,"GBC")</f>
         <v>6</v>
       </c>
       <c r="V21" s="70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W21" s="71">
         <f>COUNTIF(E:E,"Pinball")</f>
@@ -8062,13 +8062,13 @@
         <v>368</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>21</v>
@@ -8100,14 +8100,14 @@
         <v>386</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q22" s="15">
         <f>COUNTIF(C:C,"GC")</f>
         <v>4</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="T22" s="15">
         <f>COUNTIF(D:D,"PS2")</f>
@@ -8127,13 +8127,13 @@
         <v>367</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>22</v>
@@ -8157,7 +8157,7 @@
         <v>38</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q23" s="15">
         <f>COUNTIF(C:C,"GBC")</f>
@@ -8177,13 +8177,13 @@
         <v>366</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
@@ -8208,20 +8208,20 @@
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N24" s="44" t="s">
         <v>51</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q24" s="15">
         <f>COUNTIF(C:C,"X One")</f>
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T24" s="15">
         <f>COUNTIF(D:D,"GC")</f>
@@ -8234,7 +8234,7 @@
         <v>365</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>20</v>
@@ -8265,21 +8265,21 @@
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="49" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N25" s="42">
         <f>COUNTIFS(B:B,"*[P]*")</f>
         <v>20</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q25" s="15">
         <f>COUNTIF(C:C,"PS2")</f>
         <v>0</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T25" s="15">
         <f>COUNTIF(D:D,"MD")</f>
@@ -8292,13 +8292,13 @@
         <v>364</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>27</v>
@@ -8323,21 +8323,21 @@
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="48" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N26" s="42">
         <f>COUNTIFS(B:B,"*[D]*")</f>
         <v>4</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q26" s="15">
         <f>COUNTIF(C:C,"NES")</f>
         <v>0</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T26" s="15">
         <f>COUNTIF(D:D,"NES")</f>
@@ -8350,7 +8350,7 @@
         <v>363</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>20</v>
@@ -8381,21 +8381,21 @@
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="45" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N27" s="42">
         <f>N29-N28</f>
         <v>334</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q27" s="15">
         <f>COUNTIF(C:C,"MD")</f>
         <v>0</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T27" s="15">
         <f>COUNTIF(D:D,"X One")</f>
@@ -8408,13 +8408,13 @@
         <v>362</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>27</v>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N28" s="42">
         <f>COUNTIFS(B:B,"*(*")</f>
@@ -8466,13 +8466,13 @@
         <v>361</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>23</v>
@@ -8496,7 +8496,7 @@
         <v>37</v>
       </c>
       <c r="M29" s="43" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N29" s="47">
         <f>COUNT(A:A)</f>
@@ -8509,7 +8509,7 @@
         <v>360</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>20</v>
@@ -8533,7 +8533,7 @@
         <v>32</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>37</v>
@@ -8548,7 +8548,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="T30" s="38" t="s">
         <v>0</v>
@@ -8560,13 +8560,13 @@
         <v>359</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>21</v>
@@ -8597,14 +8597,14 @@
         <v>0</v>
       </c>
       <c r="P31" s="33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q31" s="15" cm="1">
         <f t="array" ref="Q31">SUM(SUMIF($P$4:$P$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$Q$4:$Q$27))</f>
         <v>198</v>
       </c>
       <c r="S31" s="33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T31" s="15" cm="1">
         <f t="array" ref="T31">SUM(SUMIF($S$4:$S$27,{"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES"},$T$4:$T$27))</f>
@@ -8617,13 +8617,13 @@
         <v>358</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>23</v>
@@ -8648,21 +8648,21 @@
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="52" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N32" s="42">
         <f>COUNTIF(K:K,"Sim")</f>
         <v>290</v>
       </c>
       <c r="P32" s="58" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q32" s="15" cm="1">
         <f t="array" ref="Q32">SUM(SUMIF($P$4:$P$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$Q$4:$Q$27))</f>
         <v>87</v>
       </c>
       <c r="S32" s="58" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="T32" s="15" cm="1">
         <f t="array" ref="T32">SUM(SUMIF($S$4:$S$27,{"PS1";"PS2";"PS3";"PS4";"PSP";"Vita"},$T$4:$T$27))</f>
@@ -8675,13 +8675,13 @@
         <v>357</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>23</v>
@@ -8706,21 +8706,21 @@
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="53" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N33" s="42">
         <f>COUNTIF(K:K,"Não")</f>
         <v>96</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q33" s="15" cm="1">
         <f t="array" ref="Q33">SUM(SUMIF($P$4:$P$27,{"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>15</v>
       </c>
       <c r="S33" s="59" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="T33" s="15" cm="1">
         <f t="array" ref="T33">SUM(SUMIF($S$4:$S$27,{"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8733,13 +8733,13 @@
         <v>356</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>24</v>
@@ -8791,13 +8791,13 @@
         <v>355</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>23</v>
@@ -8824,14 +8824,14 @@
       <c r="M35"/>
       <c r="N35"/>
       <c r="P35" s="62" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q35" s="15" cm="1">
         <f t="array" ref="Q35">SUM($Q$4:$Q$27)-SUM(SUMIF($P$4:$P$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$Q$4:$Q$27))</f>
         <v>0</v>
       </c>
       <c r="S35" s="62" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="T35" s="15" cm="1">
         <f t="array" ref="T35">SUM($T$4:$T$27)-SUM(SUMIF($S$4:$S$27,{"PC";"Switch";"Switch 2";"3DS";"DS";"Wii";"Wii U";"SNES";"N64";"GBA";"GB";"GBC";"GC";"NES";"PS1";"PS2";"PS3";"PS4";"PSP";"Vita";"X Series";"X One";"X 360"},$T$4:$T$27))</f>
@@ -8844,13 +8844,13 @@
         <v>354</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>27</v>
@@ -8897,13 +8897,13 @@
         <v>353</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>24</v>
@@ -8937,13 +8937,13 @@
         <v>352</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>29</v>
@@ -8971,10 +8971,10 @@
         <v>53</v>
       </c>
       <c r="N38" s="55" t="s">
+        <v>489</v>
+      </c>
+      <c r="O38" s="82" t="s">
         <v>490</v>
-      </c>
-      <c r="O38" s="82" t="s">
-        <v>491</v>
       </c>
       <c r="P38" s="83"/>
     </row>
@@ -8984,13 +8984,13 @@
         <v>351</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>23</v>
@@ -9033,13 +9033,13 @@
         <v>350</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>65</v>
@@ -9082,13 +9082,13 @@
         <v>349</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>22</v>
@@ -9131,13 +9131,13 @@
         <v>348</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>23</v>
@@ -9180,13 +9180,13 @@
         <v>347</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>21</v>
@@ -9228,13 +9228,13 @@
         <v>346</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>23</v>
@@ -9276,13 +9276,13 @@
         <v>345</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>23</v>
@@ -9324,13 +9324,13 @@
         <v>344</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>28</v>
@@ -9372,13 +9372,13 @@
         <v>343</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>107</v>
@@ -9396,7 +9396,7 @@
         <v>33</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>37</v>
@@ -9423,10 +9423,10 @@
         <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>21</v>
@@ -9468,13 +9468,13 @@
         <v>341</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>21</v>
@@ -9516,13 +9516,13 @@
         <v>340</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>23</v>
@@ -9564,7 +9564,7 @@
         <v>339</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>20</v>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="O51" s="76">
         <f>SUMIFS($G:$G, $F:$F, "&gt;="&amp;DATE(M51,1,1), $F:$F, "&lt;="&amp;DATE(M51,12,31))</f>
-        <v>40.547222222222231</v>
+        <v>40.547222222222224</v>
       </c>
       <c r="P51" s="77"/>
     </row>
@@ -9612,7 +9612,7 @@
         <v>338</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>20</v>
@@ -9636,7 +9636,7 @@
         <v>32</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>37</v>
@@ -9660,13 +9660,13 @@
         <v>337</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>30</v>
@@ -9696,7 +9696,7 @@
         <v>336</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>20</v>
@@ -9732,13 +9732,13 @@
         <v>335</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>69</v>
@@ -9756,7 +9756,7 @@
         <v>32</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>38</v>
@@ -9768,13 +9768,13 @@
         <v>334</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>69</v>
@@ -9792,7 +9792,7 @@
         <v>32</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>38</v>
@@ -9804,13 +9804,13 @@
         <v>333</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>69</v>
@@ -9828,7 +9828,7 @@
         <v>32</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>38</v>
@@ -9840,13 +9840,13 @@
         <v>332</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>69</v>
@@ -9864,7 +9864,7 @@
         <v>32</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>38</v>
@@ -9876,13 +9876,13 @@
         <v>331</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>69</v>
@@ -9900,7 +9900,7 @@
         <v>32</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>38</v>
@@ -9912,13 +9912,13 @@
         <v>330</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>69</v>
@@ -9936,7 +9936,7 @@
         <v>32</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>38</v>
@@ -9954,7 +9954,7 @@
         <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>22</v>
@@ -9984,13 +9984,13 @@
         <v>328</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>69</v>
@@ -10008,7 +10008,7 @@
         <v>32</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>38</v>
@@ -10020,13 +10020,13 @@
         <v>327</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>69</v>
@@ -10044,7 +10044,7 @@
         <v>32</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>37</v>
@@ -10062,7 +10062,7 @@
         <v>20</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>21</v>
@@ -10092,7 +10092,7 @@
         <v>325</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>20</v>
@@ -10128,7 +10128,7 @@
         <v>324</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>20</v>
@@ -10164,7 +10164,7 @@
         <v>323</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>20</v>
@@ -10200,7 +10200,7 @@
         <v>322</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>20</v>
@@ -10236,7 +10236,7 @@
         <v>321</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>20</v>
@@ -10260,7 +10260,7 @@
         <v>32</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>37</v>
@@ -10272,7 +10272,7 @@
         <v>320</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
@@ -10308,7 +10308,7 @@
         <v>319</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>20</v>
@@ -10344,7 +10344,7 @@
         <v>318</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>20</v>
@@ -10368,7 +10368,7 @@
         <v>33</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>37</v>
@@ -10380,13 +10380,13 @@
         <v>317</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>22</v>
@@ -10416,13 +10416,13 @@
         <v>316</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>27</v>
@@ -10452,7 +10452,7 @@
         <v>315</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>20</v>
@@ -10476,7 +10476,7 @@
         <v>33</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>37</v>
@@ -10488,13 +10488,13 @@
         <v>314</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>69</v>
@@ -10512,7 +10512,7 @@
         <v>33</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>38</v>
@@ -10524,16 +10524,16 @@
         <v>313</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F77" s="5">
         <v>45260</v>
@@ -10548,7 +10548,7 @@
         <v>34</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>38</v>
@@ -10560,13 +10560,13 @@
         <v>312</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>21</v>
@@ -10596,7 +10596,7 @@
         <v>311</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>20</v>
@@ -10632,13 +10632,13 @@
         <v>310</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>21</v>
@@ -10668,13 +10668,13 @@
         <v>309</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>23</v>
@@ -10704,13 +10704,13 @@
         <v>308</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>21</v>
@@ -10740,13 +10740,13 @@
         <v>307</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>21</v>
@@ -10776,13 +10776,13 @@
         <v>306</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>23</v>
@@ -10812,13 +10812,13 @@
         <v>305</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>23</v>
@@ -10848,13 +10848,13 @@
         <v>304</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>157</v>
@@ -10884,13 +10884,13 @@
         <v>303</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -10920,13 +10920,13 @@
         <v>302</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>21</v>
@@ -10956,13 +10956,13 @@
         <v>301</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>23</v>
@@ -10992,13 +10992,13 @@
         <v>300</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>23</v>
@@ -11028,13 +11028,13 @@
         <v>299</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>69</v>
@@ -11052,7 +11052,7 @@
         <v>33</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>38</v>
@@ -11064,13 +11064,13 @@
         <v>298</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>23</v>
@@ -11100,13 +11100,13 @@
         <v>297</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>22</v>
@@ -11136,13 +11136,13 @@
         <v>296</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>107</v>
@@ -11160,7 +11160,7 @@
         <v>34</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K94" s="1" t="s">
         <v>37</v>
@@ -11172,13 +11172,13 @@
         <v>295</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>107</v>
@@ -11196,7 +11196,7 @@
         <v>32</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>37</v>
@@ -11208,13 +11208,13 @@
         <v>294</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>22</v>
@@ -11244,7 +11244,7 @@
         <v>293</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>20</v>
@@ -11280,13 +11280,13 @@
         <v>292</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>22</v>
@@ -11316,13 +11316,13 @@
         <v>291</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>21</v>
@@ -11352,13 +11352,13 @@
         <v>290</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>27</v>
@@ -11388,13 +11388,13 @@
         <v>289</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>30</v>
@@ -11412,7 +11412,7 @@
         <v>34</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>37</v>
@@ -11424,13 +11424,13 @@
         <v>288</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>30</v>
@@ -11448,7 +11448,7 @@
         <v>34</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>37</v>
@@ -11460,7 +11460,7 @@
         <v>287</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>20</v>
@@ -11496,7 +11496,7 @@
         <v>286</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>20</v>
@@ -11505,7 +11505,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F104" s="5">
         <v>45011</v>
@@ -11532,7 +11532,7 @@
         <v>285</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>20</v>
@@ -11568,13 +11568,13 @@
         <v>284</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>23</v>
@@ -11604,13 +11604,13 @@
         <v>283</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>23</v>
@@ -11640,13 +11640,13 @@
         <v>282</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -11664,7 +11664,7 @@
         <v>52</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>37</v>
@@ -11676,13 +11676,13 @@
         <v>281</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>23</v>
@@ -11712,13 +11712,13 @@
         <v>280</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>23</v>
@@ -11748,7 +11748,7 @@
         <v>279</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>20</v>
@@ -11784,7 +11784,7 @@
         <v>278</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>20</v>
@@ -11820,7 +11820,7 @@
         <v>277</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>20</v>
@@ -11856,7 +11856,7 @@
         <v>276</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>20</v>
@@ -11892,13 +11892,13 @@
         <v>275</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>24</v>
@@ -11928,7 +11928,7 @@
         <v>274</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>20</v>
@@ -11964,7 +11964,7 @@
         <v>273</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>20</v>
@@ -12000,7 +12000,7 @@
         <v>272</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>20</v>
@@ -12036,13 +12036,13 @@
         <v>271</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>23</v>
@@ -12072,7 +12072,7 @@
         <v>270</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>20</v>
@@ -12108,7 +12108,7 @@
         <v>269</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>20</v>
@@ -12144,7 +12144,7 @@
         <v>268</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>20</v>
@@ -12180,7 +12180,7 @@
         <v>267</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>20</v>
@@ -12216,7 +12216,7 @@
         <v>266</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>20</v>
@@ -12252,7 +12252,7 @@
         <v>265</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>20</v>
@@ -12288,7 +12288,7 @@
         <v>264</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>20</v>
@@ -12297,7 +12297,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F126" s="5">
         <v>44757</v>
@@ -12324,7 +12324,7 @@
         <v>263</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>20</v>
@@ -12360,7 +12360,7 @@
         <v>262</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>20</v>
@@ -12396,7 +12396,7 @@
         <v>261</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>20</v>
@@ -12432,7 +12432,7 @@
         <v>260</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>20</v>
@@ -12468,7 +12468,7 @@
         <v>259</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>20</v>
@@ -12504,7 +12504,7 @@
         <v>258</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>20</v>
@@ -12540,7 +12540,7 @@
         <v>257</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>20</v>
@@ -12576,7 +12576,7 @@
         <v>256</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>20</v>
@@ -12612,7 +12612,7 @@
         <v>255</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>20</v>
@@ -12648,7 +12648,7 @@
         <v>254</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>20</v>
@@ -12672,7 +12672,7 @@
         <v>32</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K136" s="1" t="s">
         <v>37</v>
@@ -12684,7 +12684,7 @@
         <v>253</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>20</v>
@@ -12720,7 +12720,7 @@
         <v>252</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>20</v>
@@ -12756,7 +12756,7 @@
         <v>251</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>20</v>
@@ -12792,7 +12792,7 @@
         <v>250</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>20</v>
@@ -12801,7 +12801,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F140" s="5">
         <v>44672</v>
@@ -12828,7 +12828,7 @@
         <v>249</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>20</v>
@@ -12864,13 +12864,13 @@
         <v>248</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>23</v>
@@ -12900,13 +12900,13 @@
         <v>247</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>23</v>
@@ -12936,13 +12936,13 @@
         <v>246</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>157</v>
@@ -12960,7 +12960,7 @@
         <v>33</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>38</v>
@@ -12972,13 +12972,13 @@
         <v>245</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>24</v>
@@ -13008,13 +13008,13 @@
         <v>244</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>24</v>
@@ -13044,13 +13044,13 @@
         <v>243</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>87</v>
@@ -13080,13 +13080,13 @@
         <v>242</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>29</v>
@@ -13116,13 +13116,13 @@
         <v>241</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>23</v>
@@ -13152,13 +13152,13 @@
         <v>240</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>120</v>
@@ -13188,13 +13188,13 @@
         <v>239</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>27</v>
@@ -13224,13 +13224,13 @@
         <v>238</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>22</v>
@@ -13260,7 +13260,7 @@
         <v>237</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>20</v>
@@ -13296,7 +13296,7 @@
         <v>236</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>20</v>
@@ -13332,16 +13332,16 @@
         <v>235</v>
       </c>
       <c r="B155" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="F155" s="5">
         <v>44318</v>
@@ -13368,13 +13368,13 @@
         <v>234</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>21</v>
@@ -13404,13 +13404,13 @@
         <v>233</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>23</v>
@@ -13440,13 +13440,13 @@
         <v>232</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>27</v>
@@ -13476,13 +13476,13 @@
         <v>231</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>30</v>
@@ -13500,7 +13500,7 @@
         <v>34</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>37</v>
@@ -13512,13 +13512,13 @@
         <v>230</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>87</v>
@@ -13548,13 +13548,13 @@
         <v>229</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>23</v>
@@ -13584,13 +13584,13 @@
         <v>228</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>107</v>
@@ -13620,16 +13620,16 @@
         <v>227</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F163" s="5">
         <v>44166</v>
@@ -13656,13 +13656,13 @@
         <v>226</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>30</v>
@@ -13692,13 +13692,13 @@
         <v>225</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>27</v>
@@ -13728,13 +13728,13 @@
         <v>224</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>23</v>
@@ -13764,13 +13764,13 @@
         <v>223</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>23</v>
@@ -13800,16 +13800,16 @@
         <v>222</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F168" s="5">
         <v>44110</v>
@@ -13836,13 +13836,13 @@
         <v>221</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>107</v>
@@ -13860,7 +13860,7 @@
         <v>33</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K169" s="1" t="s">
         <v>37</v>
@@ -13872,13 +13872,13 @@
         <v>220</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>65</v>
@@ -13908,13 +13908,13 @@
         <v>219</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>23</v>
@@ -13944,13 +13944,13 @@
         <v>218</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>23</v>
@@ -13980,13 +13980,13 @@
         <v>217</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>65</v>
@@ -14016,13 +14016,13 @@
         <v>216</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>171</v>
+        <v>514</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>23</v>
@@ -14052,13 +14052,13 @@
         <v>215</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>21</v>
@@ -14088,13 +14088,13 @@
         <v>214</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>24</v>
@@ -14127,10 +14127,10 @@
         <v>169</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>21</v>
@@ -14163,10 +14163,10 @@
         <v>168</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>157</v>
@@ -14196,13 +14196,13 @@
         <v>211</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>22</v>
@@ -14235,10 +14235,10 @@
         <v>166</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>30</v>
@@ -14271,10 +14271,10 @@
         <v>165</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>24</v>
@@ -14304,13 +14304,13 @@
         <v>208</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>22</v>
@@ -14343,10 +14343,10 @@
         <v>164</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>25</v>
@@ -14379,10 +14379,10 @@
         <v>163</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>87</v>
@@ -14415,10 +14415,10 @@
         <v>162</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>21</v>
@@ -14451,10 +14451,10 @@
         <v>161</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>24</v>
@@ -14487,10 +14487,10 @@
         <v>160</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>22</v>
@@ -14520,13 +14520,13 @@
         <v>202</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>65</v>
@@ -14559,10 +14559,10 @@
         <v>159</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>30</v>
@@ -14592,13 +14592,13 @@
         <v>200</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>65</v>
@@ -14628,13 +14628,13 @@
         <v>199</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>24</v>
@@ -14667,10 +14667,10 @@
         <v>155</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>23</v>
@@ -14703,10 +14703,10 @@
         <v>154</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>30</v>
@@ -14736,13 +14736,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>30</v>
@@ -14772,13 +14772,13 @@
         <v>195</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>157</v>
@@ -14796,7 +14796,7 @@
         <v>33</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K195" s="1" t="s">
         <v>37</v>
@@ -14811,10 +14811,10 @@
         <v>153</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>24</v>
@@ -14847,10 +14847,10 @@
         <v>152</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>21</v>
@@ -14880,13 +14880,13 @@
         <v>192</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>21</v>
@@ -14916,13 +14916,13 @@
         <v>191</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>120</v>
@@ -14988,7 +14988,7 @@
         <v>189</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>156</v>
@@ -15099,10 +15099,10 @@
         <v>147</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>23</v>
@@ -15135,10 +15135,10 @@
         <v>146</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>87</v>
@@ -15171,10 +15171,10 @@
         <v>145</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>23</v>
@@ -15207,10 +15207,10 @@
         <v>144</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>87</v>
@@ -15243,10 +15243,10 @@
         <v>143</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>21</v>
@@ -15279,10 +15279,10 @@
         <v>150</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>23</v>
@@ -15312,13 +15312,13 @@
         <v>180</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>23</v>
@@ -15348,13 +15348,13 @@
         <v>179</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>21</v>
@@ -15387,10 +15387,10 @@
         <v>142</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>23</v>
@@ -15423,10 +15423,10 @@
         <v>141</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>23</v>
@@ -15459,10 +15459,10 @@
         <v>140</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>23</v>
@@ -15495,10 +15495,10 @@
         <v>139</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>23</v>
@@ -15531,10 +15531,10 @@
         <v>138</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>23</v>
@@ -15567,10 +15567,10 @@
         <v>137</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>23</v>
@@ -15600,13 +15600,13 @@
         <v>172</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>21</v>
@@ -15639,10 +15639,10 @@
         <v>136</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>23</v>
@@ -15672,13 +15672,13 @@
         <v>170</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>23</v>
@@ -15711,10 +15711,10 @@
         <v>135</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>23</v>
@@ -15744,13 +15744,13 @@
         <v>168</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>23</v>
@@ -15783,10 +15783,10 @@
         <v>134</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>23</v>
@@ -15819,10 +15819,10 @@
         <v>133</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>107</v>
@@ -15855,10 +15855,10 @@
         <v>132</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>23</v>
@@ -15888,13 +15888,13 @@
         <v>164</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>23</v>
@@ -15924,13 +15924,13 @@
         <v>163</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>23</v>
@@ -15960,13 +15960,13 @@
         <v>162</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>23</v>
@@ -15999,10 +15999,10 @@
         <v>131</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>23</v>
@@ -16035,10 +16035,10 @@
         <v>130</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>23</v>
@@ -16071,10 +16071,10 @@
         <v>129</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>23</v>
@@ -16107,10 +16107,10 @@
         <v>128</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>23</v>
@@ -16143,10 +16143,10 @@
         <v>127</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>23</v>
@@ -16176,13 +16176,13 @@
         <v>156</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>22</v>
@@ -16215,10 +16215,10 @@
         <v>126</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>21</v>
@@ -16248,13 +16248,13 @@
         <v>154</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>22</v>
@@ -16284,13 +16284,13 @@
         <v>153</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>22</v>
@@ -16323,10 +16323,10 @@
         <v>125</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>23</v>
@@ -16359,10 +16359,10 @@
         <v>124</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>23</v>
@@ -16395,10 +16395,10 @@
         <v>123</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>23</v>
@@ -16431,10 +16431,10 @@
         <v>122</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>22</v>
@@ -16464,13 +16464,13 @@
         <v>148</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>23</v>
@@ -16503,10 +16503,10 @@
         <v>121</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>23</v>
@@ -16539,10 +16539,10 @@
         <v>119</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>23</v>
@@ -16572,13 +16572,13 @@
         <v>145</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>27</v>
@@ -16611,10 +16611,10 @@
         <v>117</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>120</v>
@@ -16644,13 +16644,13 @@
         <v>143</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>21</v>
@@ -16683,10 +16683,10 @@
         <v>116</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>23</v>
@@ -16716,13 +16716,13 @@
         <v>141</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>23</v>
@@ -16755,10 +16755,10 @@
         <v>115</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>23</v>
@@ -16791,10 +16791,10 @@
         <v>114</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>28</v>
@@ -16827,10 +16827,10 @@
         <v>113</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>23</v>
@@ -16863,10 +16863,10 @@
         <v>112</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>23</v>
@@ -16899,10 +16899,10 @@
         <v>111</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>23</v>
@@ -16935,10 +16935,10 @@
         <v>110</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>22</v>
@@ -16971,10 +16971,10 @@
         <v>109</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>21</v>
@@ -17007,10 +17007,10 @@
         <v>106</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>21</v>
@@ -17043,10 +17043,10 @@
         <v>105</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>30</v>
@@ -17079,10 +17079,10 @@
         <v>104</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>30</v>
@@ -17115,10 +17115,10 @@
         <v>103</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>22</v>
@@ -17151,10 +17151,10 @@
         <v>102</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>107</v>
@@ -17187,10 +17187,10 @@
         <v>100</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>65</v>
@@ -17223,10 +17223,10 @@
         <v>99</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>27</v>
@@ -17256,7 +17256,7 @@
         <v>126</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>20</v>
@@ -17295,10 +17295,10 @@
         <v>98</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>23</v>
@@ -17328,13 +17328,13 @@
         <v>124</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>27</v>
@@ -17367,10 +17367,10 @@
         <v>96</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>27</v>
@@ -17403,10 +17403,10 @@
         <v>95</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>21</v>
@@ -17436,13 +17436,13 @@
         <v>121</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>21</v>
@@ -17475,10 +17475,10 @@
         <v>94</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>21</v>
@@ -17508,13 +17508,13 @@
         <v>119</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>27</v>
@@ -17547,10 +17547,10 @@
         <v>93</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>24</v>
@@ -17583,10 +17583,10 @@
         <v>92</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>23</v>
@@ -17619,10 +17619,10 @@
         <v>90</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>27</v>
@@ -17655,10 +17655,10 @@
         <v>89</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>23</v>
@@ -17691,10 +17691,10 @@
         <v>88</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>24</v>
@@ -17724,13 +17724,13 @@
         <v>113</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>22</v>
@@ -17763,10 +17763,10 @@
         <v>86</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>23</v>
@@ -17799,10 +17799,10 @@
         <v>85</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>23</v>
@@ -17835,10 +17835,10 @@
         <v>84</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>28</v>
@@ -17871,10 +17871,10 @@
         <v>83</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>23</v>
@@ -17907,10 +17907,10 @@
         <v>82</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>87</v>
@@ -17943,10 +17943,10 @@
         <v>81</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>23</v>
@@ -17979,10 +17979,10 @@
         <v>80</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>23</v>
@@ -18015,10 +18015,10 @@
         <v>79</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>28</v>
@@ -18051,10 +18051,10 @@
         <v>78</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>23</v>
@@ -18087,10 +18087,10 @@
         <v>77</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>21</v>
@@ -18120,13 +18120,13 @@
         <v>102</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>65</v>
@@ -18159,10 +18159,10 @@
         <v>75</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>24</v>
@@ -18195,10 +18195,10 @@
         <v>76</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>24</v>
@@ -18231,10 +18231,10 @@
         <v>74</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>24</v>
@@ -18267,10 +18267,10 @@
         <v>73</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>23</v>
@@ -18303,10 +18303,10 @@
         <v>72</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>23</v>
@@ -18339,10 +18339,10 @@
         <v>68</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>23</v>
@@ -18375,10 +18375,10 @@
         <v>67</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>30</v>
@@ -18408,13 +18408,13 @@
         <v>94</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>22</v>
@@ -18444,13 +18444,13 @@
         <v>93</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C297" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>22</v>
@@ -18480,13 +18480,13 @@
         <v>92</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>69</v>
@@ -18516,13 +18516,13 @@
         <v>91</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>22</v>
@@ -18555,10 +18555,10 @@
         <v>64</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>23</v>
@@ -18591,10 +18591,10 @@
         <v>63</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>65</v>
@@ -18627,10 +18627,10 @@
         <v>62</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>22</v>
@@ -18663,10 +18663,10 @@
         <v>61</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>21</v>
@@ -18699,10 +18699,10 @@
         <v>60</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>21</v>
@@ -18735,10 +18735,10 @@
         <v>58</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>21</v>
@@ -18771,10 +18771,10 @@
         <v>91</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>27</v>
@@ -18807,10 +18807,10 @@
         <v>57</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>23</v>
@@ -18843,10 +18843,10 @@
         <v>56</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>21</v>
@@ -18876,13 +18876,13 @@
         <v>81</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>21</v>
@@ -18915,10 +18915,10 @@
         <v>55</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>28</v>
@@ -18951,10 +18951,10 @@
         <v>54</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>27</v>
@@ -19023,10 +19023,10 @@
         <v>18</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>23</v>
@@ -19056,13 +19056,13 @@
         <v>76</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>22</v>
@@ -19092,13 +19092,13 @@
         <v>75</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>21</v>
@@ -19128,7 +19128,7 @@
         <v>74</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>20</v>
@@ -19164,13 +19164,13 @@
         <v>73</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>23</v>
@@ -19203,10 +19203,10 @@
         <v>17</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>29</v>
@@ -19239,10 +19239,10 @@
         <v>16</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>28</v>
@@ -19275,10 +19275,10 @@
         <v>15</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>27</v>
@@ -19311,10 +19311,10 @@
         <v>14</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>23</v>
@@ -19347,10 +19347,10 @@
         <v>13</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>23</v>
@@ -19452,7 +19452,7 @@
         <v>65</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>20</v>
@@ -19524,7 +19524,7 @@
         <v>63</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>20</v>
@@ -19560,7 +19560,7 @@
         <v>62</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>20</v>
@@ -19599,10 +19599,10 @@
         <v>8</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>23</v>
@@ -19635,10 +19635,10 @@
         <v>7</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>23</v>
@@ -19671,10 +19671,10 @@
         <v>6</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>24</v>
@@ -19704,13 +19704,13 @@
         <v>58</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>27</v>
@@ -19740,13 +19740,13 @@
         <v>57</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>65</v>
@@ -19776,13 +19776,13 @@
         <v>56</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>29</v>
@@ -19800,7 +19800,7 @@
         <v>52</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K334" s="1" t="s">
         <v>37</v>
@@ -19812,13 +19812,13 @@
         <v>55</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>29</v>
@@ -19836,7 +19836,7 @@
         <v>32</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K335" s="1" t="s">
         <v>37</v>
@@ -19848,13 +19848,13 @@
         <v>54</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>23</v>
@@ -19884,13 +19884,13 @@
         <v>53</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>65</v>
@@ -19908,7 +19908,7 @@
         <v>34</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K337" s="1" t="s">
         <v>37</v>
@@ -19920,13 +19920,13 @@
         <v>52</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>21</v>
@@ -19956,13 +19956,13 @@
         <v>51</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>157</v>
@@ -19980,7 +19980,7 @@
         <v>34</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K339" s="1" t="s">
         <v>37</v>
@@ -19992,13 +19992,13 @@
         <v>50</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>27</v>
@@ -20028,13 +20028,13 @@
         <v>49</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>27</v>
@@ -20064,13 +20064,13 @@
         <v>48</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>27</v>
@@ -20100,13 +20100,13 @@
         <v>47</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>27</v>
@@ -20136,13 +20136,13 @@
         <v>46</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>27</v>
@@ -20172,13 +20172,13 @@
         <v>45</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>27</v>
@@ -20208,13 +20208,13 @@
         <v>44</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>21</v>
@@ -20244,13 +20244,13 @@
         <v>43</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>27</v>
@@ -20280,13 +20280,13 @@
         <v>42</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>27</v>
@@ -20316,13 +20316,13 @@
         <v>41</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>65</v>
@@ -20352,13 +20352,13 @@
         <v>40</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>22</v>
@@ -20388,13 +20388,13 @@
         <v>39</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>27</v>
@@ -20424,13 +20424,13 @@
         <v>38</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>28</v>
@@ -20460,13 +20460,13 @@
         <v>37</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>30</v>
@@ -20496,13 +20496,13 @@
         <v>36</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>27</v>
@@ -20532,13 +20532,13 @@
         <v>35</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>65</v>
@@ -20568,13 +20568,13 @@
         <v>34</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>22</v>
@@ -20604,13 +20604,13 @@
         <v>33</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>30</v>
@@ -20628,7 +20628,7 @@
         <v>32</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K357" s="1" t="s">
         <v>37</v>
@@ -20640,13 +20640,13 @@
         <v>32</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>22</v>
@@ -20676,13 +20676,13 @@
         <v>31</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>22</v>
@@ -20712,13 +20712,13 @@
         <v>30</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>22</v>
@@ -20748,13 +20748,13 @@
         <v>29</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>22</v>
@@ -20784,13 +20784,13 @@
         <v>28</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>28</v>
@@ -20823,10 +20823,10 @@
         <v>122</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>22</v>
@@ -20856,13 +20856,13 @@
         <v>26</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>21</v>
@@ -20892,13 +20892,13 @@
         <v>25</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>30</v>
@@ -20916,7 +20916,7 @@
         <v>32</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K365" s="1" t="s">
         <v>37</v>
@@ -20928,13 +20928,13 @@
         <v>24</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>27</v>
@@ -20964,13 +20964,13 @@
         <v>23</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>27</v>
@@ -21000,13 +21000,13 @@
         <v>22</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>27</v>
@@ -21036,13 +21036,13 @@
         <v>21</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>27</v>
@@ -21072,13 +21072,13 @@
         <v>20</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>65</v>
@@ -21108,13 +21108,13 @@
         <v>19</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>27</v>
@@ -21144,13 +21144,13 @@
         <v>18</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>30</v>
@@ -21180,13 +21180,13 @@
         <v>17</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>22</v>
@@ -21216,13 +21216,13 @@
         <v>16</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>120</v>
@@ -21252,13 +21252,13 @@
         <v>15</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>23</v>
@@ -21288,13 +21288,13 @@
         <v>14</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>22</v>
@@ -21324,13 +21324,13 @@
         <v>13</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>30</v>
@@ -21363,10 +21363,10 @@
         <v>167</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>22</v>
@@ -21396,25 +21396,25 @@
         <v>11</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F379" s="5">
-        <v>41893</v>
+        <v>41895</v>
       </c>
       <c r="G379" s="28">
-        <v>0.83333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="H379" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>32</v>
@@ -21423,7 +21423,7 @@
         <v>36</v>
       </c>
       <c r="K379" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.2">
@@ -21432,25 +21432,25 @@
         <v>10</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>26</v>
+        <v>443</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F380" s="5">
-        <v>41895</v>
+        <v>41893</v>
       </c>
       <c r="G380" s="28">
-        <v>0.625</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H380" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>32</v>
@@ -21459,7 +21459,7 @@
         <v>36</v>
       </c>
       <c r="K380" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="381" spans="1:11" ht="15" x14ac:dyDescent="0.25">
@@ -21468,13 +21468,13 @@
         <v>9</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>25</v>
@@ -21504,13 +21504,13 @@
         <v>8</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>22</v>
@@ -21543,10 +21543,10 @@
         <v>158</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>65</v>
@@ -21576,25 +21576,25 @@
         <v>6</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>496</v>
+        <v>9</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F384" s="5">
-        <v>41723</v>
+        <v>41743</v>
       </c>
       <c r="G384" s="28">
-        <v>1.125</v>
+        <v>1.5416666666666667</v>
       </c>
       <c r="H384" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>32</v>
@@ -21603,7 +21603,7 @@
         <v>36</v>
       </c>
       <c r="K384" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.2">
@@ -21612,31 +21612,31 @@
         <v>5</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F385" s="5">
-        <v>41713</v>
+        <v>41723</v>
       </c>
       <c r="G385" s="28">
-        <v>0.10416666666666667</v>
+        <v>1.125</v>
       </c>
       <c r="H385" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K385" s="1" t="s">
         <v>38</v>
@@ -21648,22 +21648,22 @@
         <v>4</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F386" s="5">
-        <v>41743</v>
+        <v>41720</v>
       </c>
       <c r="G386" s="28">
-        <v>1.5416666666666667</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H386" s="1">
         <v>10</v>
@@ -21684,31 +21684,31 @@
         <v>3</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>97</v>
+        <v>445</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F387" s="5">
         <v>41720</v>
       </c>
       <c r="G387" s="28">
-        <v>0.83333333333333337</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="H387" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>36</v>
+        <v>436</v>
       </c>
       <c r="K387" s="1" t="s">
         <v>37</v>
@@ -21720,34 +21720,34 @@
         <v>2</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>446</v>
+        <v>500</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F388" s="5">
-        <v>41720</v>
+        <v>41713</v>
       </c>
       <c r="G388" s="28">
-        <v>5.083333333333333</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="H388" s="1">
         <v>7</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>437</v>
+        <v>71</v>
       </c>
       <c r="K388" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.2">
@@ -21756,13 +21756,13 @@
         <v>1</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>23</v>
@@ -21818,22 +21818,22 @@
     <mergeCell ref="O51:P51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 O30:O57 M37:N53 R26:R1048576 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>OR(ISNUMBER(FIND("NES",C1)),    ISNUMBER(FIND("SNES",C1)),    ISNUMBER(FIND("N64",C1)),    ISNUMBER(FIND("GC",C1)),    ISNUMBER(FIND("Wii",C1)),    ISNUMBER(FIND("Wii U",C1)),    ISNUMBER(FIND("Switch",C1)),    ISNUMBER(FIND("Switch 2",C1)),    ISNUMBER(FIND("GB",C1)),    ISNUMBER(FIND("GBC",C1)),    ISNUMBER(FIND("GBA",C1)),    ISNUMBER(FIND("DS",C1)),    ISNUMBER(FIND("3DS",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 S26:T29 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 O30:O57 M37:N53 S26:T29 R26:R1048576 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
     <cfRule type="expression" dxfId="23" priority="18">
       <formula>OR(ISNUMBER(FIND("X One",C1)),    ISNUMBER(FIND("X Series",C1)),    ISNUMBER(FIND("X 360",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 O30:O57 M37:N53 R26:R1048576 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
     <cfRule type="expression" dxfId="22" priority="17">
       <formula>OR(ISNUMBER(FIND("PS1",C1)),    ISNUMBER(FIND("PS2",C1)),    ISNUMBER(FIND("PS3",C1)),    ISNUMBER(FIND("PS4",C1)),    ISNUMBER(FIND("PSP",C1)),    ISNUMBER(FIND("Vita",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 S26:T29 R26:R1048576 O30:O57 M37:N53 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
+  <conditionalFormatting sqref="C1:T2 M3:N22 V3:W22 O3:T25 M24:N34 O26:Q29 S26:T29 O30:O57 M37:N53 R26:R1048576 S39:T1048576 Q51:Q1048576 M58:P1048576 C3:L1048576">
     <cfRule type="expression" dxfId="21" priority="19">
       <formula>ISNUMBER(FIND("PC",C1))</formula>
     </cfRule>
@@ -21940,59 +21940,59 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
       <c r="F2" s="84" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G2" s="84"/>
       <c r="H2" s="84"/>
       <c r="J2" s="84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K2" s="84"/>
       <c r="L2" s="84"/>
       <c r="N2" s="84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O2" s="84"/>
       <c r="P2" s="84"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>1</v>
@@ -22006,7 +22006,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F4" s="22">
         <v>1</v>
@@ -22024,7 +22024,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N4" s="22">
         <v>1</v>
@@ -22033,7 +22033,7 @@
         <v>11</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22053,7 +22053,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J5" s="22">
         <v>2</v>
@@ -22062,7 +22062,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N5" s="22">
         <v>2</v>
@@ -22071,7 +22071,7 @@
         <v>10</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22082,7 +22082,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F6" s="22">
         <v>3</v>
@@ -22091,7 +22091,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J6" s="22">
         <v>3</v>
@@ -22100,7 +22100,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N6" s="22">
         <v>3</v>
@@ -22109,7 +22109,7 @@
         <v>10</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22120,7 +22120,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F7" s="22">
         <v>4</v>
@@ -22129,7 +22129,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J7" s="22">
         <v>4</v>
@@ -22138,7 +22138,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N7" s="22">
         <v>4</v>
@@ -22147,7 +22147,7 @@
         <v>10</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22158,7 +22158,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F8" s="22">
         <v>5</v>
@@ -22167,7 +22167,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J8" s="22">
         <v>5</v>
@@ -22176,7 +22176,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N8" s="22">
         <v>5</v>
@@ -22185,7 +22185,7 @@
         <v>10</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22205,7 +22205,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J9" s="22">
         <v>6</v>
@@ -22214,7 +22214,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N9" s="22">
         <v>6</v>
@@ -22223,7 +22223,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22234,7 +22234,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F10" s="22">
         <v>7</v>
@@ -22243,7 +22243,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J10" s="22">
         <v>7</v>
@@ -22252,7 +22252,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N10" s="22">
         <v>7</v>
@@ -22272,7 +22272,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F11" s="22">
         <v>8</v>
@@ -22290,7 +22290,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N11" s="22">
         <v>8</v>
@@ -22299,7 +22299,7 @@
         <v>10</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22310,7 +22310,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F12" s="22">
         <v>9</v>
@@ -22337,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22348,7 +22348,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F13" s="22">
         <v>10</v>
@@ -22357,7 +22357,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J13" s="22">
         <v>10</v>
@@ -22366,7 +22366,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N13" s="22">
         <v>10</v>
@@ -22375,7 +22375,7 @@
         <v>10</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22386,7 +22386,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F14" s="22">
         <v>11</v>
@@ -22395,7 +22395,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J14" s="22">
         <v>11</v>
@@ -22413,7 +22413,7 @@
         <v>10</v>
       </c>
       <c r="P14" s="27" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22424,7 +22424,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F15" s="22">
         <v>12</v>
@@ -22433,7 +22433,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J15" s="22">
         <v>12</v>
@@ -22442,7 +22442,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N15" s="22">
         <v>12</v>
@@ -22451,7 +22451,7 @@
         <v>9</v>
       </c>
       <c r="P15" s="27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22462,7 +22462,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F16" s="22">
         <v>13</v>
@@ -22471,7 +22471,7 @@
         <v>8</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J16" s="22">
         <v>13</v>
@@ -22480,7 +22480,7 @@
         <v>7</v>
       </c>
       <c r="L16" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N16" s="22">
         <v>13</v>
@@ -22489,7 +22489,7 @@
         <v>9</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22500,7 +22500,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F17" s="22">
         <v>14</v>
@@ -22509,7 +22509,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J17" s="22">
         <v>14</v>
@@ -22518,7 +22518,7 @@
         <v>7</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N17" s="22">
         <v>14</v>
@@ -22527,7 +22527,7 @@
         <v>9</v>
       </c>
       <c r="P17" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22538,7 +22538,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F18" s="22">
         <v>15</v>
@@ -22547,7 +22547,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J18" s="22">
         <v>15</v>
@@ -22556,7 +22556,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N18" s="22">
         <v>15</v>
@@ -22565,7 +22565,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22576,7 +22576,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F19" s="22">
         <v>16</v>
@@ -22585,7 +22585,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J19" s="22">
         <v>16</v>
@@ -22594,7 +22594,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N19" s="22">
         <v>16</v>
@@ -22614,7 +22614,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F20" s="22">
         <v>17</v>
@@ -22623,7 +22623,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J20" s="22">
         <v>17</v>
@@ -22632,7 +22632,7 @@
         <v>6</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N20" s="22">
         <v>17</v>
@@ -22652,7 +22652,7 @@
         <v>7</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F21" s="22">
         <v>18</v>
@@ -22661,7 +22661,7 @@
         <v>6</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J21" s="22">
         <v>18</v>
@@ -22670,7 +22670,7 @@
         <v>6</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N21" s="22">
         <v>18</v>
@@ -22679,7 +22679,7 @@
         <v>9</v>
       </c>
       <c r="P21" s="27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22690,7 +22690,7 @@
         <v>7</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F22" s="22">
         <v>19</v>
@@ -22699,7 +22699,7 @@
         <v>6</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J22" s="22">
         <v>19</v>
@@ -22708,7 +22708,7 @@
         <v>6</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N22" s="22">
         <v>19</v>
@@ -22717,7 +22717,7 @@
         <v>9</v>
       </c>
       <c r="P22" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F23" s="22">
         <v>20</v>
@@ -22737,7 +22737,7 @@
         <v>6</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J23" s="22">
         <v>20</v>
@@ -22746,7 +22746,7 @@
         <v>6</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N23" s="22">
         <v>20</v>
@@ -22755,7 +22755,7 @@
         <v>9</v>
       </c>
       <c r="P23" s="27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22766,7 +22766,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J24" s="22">
         <v>21</v>
@@ -22775,7 +22775,7 @@
         <v>6</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N24" s="22">
         <v>21</v>
@@ -22784,7 +22784,7 @@
         <v>8</v>
       </c>
       <c r="P24" s="24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22795,7 +22795,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J25" s="22">
         <v>22</v>
@@ -22804,7 +22804,7 @@
         <v>5</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N25" s="22">
         <v>22</v>
@@ -22813,7 +22813,7 @@
         <v>8</v>
       </c>
       <c r="P25" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22824,7 +22824,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J26" s="22">
         <v>23</v>
@@ -22833,7 +22833,7 @@
         <v>4</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N26" s="22">
         <v>23</v>
@@ -22842,7 +22842,7 @@
         <v>8</v>
       </c>
       <c r="P26" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22853,7 +22853,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J27" s="22">
         <v>24</v>
@@ -22862,7 +22862,7 @@
         <v>4</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N27" s="22">
         <v>24</v>
@@ -22871,7 +22871,7 @@
         <v>8</v>
       </c>
       <c r="P27" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22882,7 +22882,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N28" s="22">
         <v>25</v>
@@ -22891,7 +22891,7 @@
         <v>8</v>
       </c>
       <c r="P28" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22902,7 +22902,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N29" s="22">
         <v>26</v>
@@ -22911,10 +22911,19 @@
         <v>8</v>
       </c>
       <c r="P29" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="22">
+        <v>27</v>
+      </c>
+      <c r="C30" s="21">
+        <v>4</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>513</v>
+      </c>
       <c r="N30" s="22">
         <v>27</v>
       </c>
@@ -22922,7 +22931,7 @@
         <v>8</v>
       </c>
       <c r="P30" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22933,7 +22942,7 @@
         <v>7</v>
       </c>
       <c r="P31" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22944,7 +22953,7 @@
         <v>7</v>
       </c>
       <c r="P32" s="24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22955,7 +22964,7 @@
         <v>7</v>
       </c>
       <c r="P33" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22966,7 +22975,7 @@
         <v>7</v>
       </c>
       <c r="P34" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22977,7 +22986,7 @@
         <v>6</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22988,7 +22997,7 @@
         <v>6</v>
       </c>
       <c r="P36" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -22999,7 +23008,7 @@
         <v>6</v>
       </c>
       <c r="P37" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="14:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -23010,7 +23019,7 @@
         <v>6</v>
       </c>
       <c r="P38" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
